--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Data/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DF53EB-78BC-D049-A9ED-0FAB71A058DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24DDF70-225D-B24F-B3CD-5BF493F06041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>No.</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t xml:space="preserve">1. Steering Stem needs replacement. 2. Oil leak from Cylinder head cover </t>
+  </si>
+  <si>
+    <t>1. Steering Stem needs bearings.</t>
   </si>
 </sst>
 </file>
@@ -947,10 +950,10 @@
         <v>19</v>
       </c>
       <c r="C14" s="5">
-        <v>9030</v>
+        <v>12036</v>
       </c>
       <c r="D14" s="5">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="E14" s="3"/>
     </row>
@@ -1028,6 +1031,9 @@
         <v>45000</v>
       </c>
       <c r="E19" s="3"/>
+      <c r="F19" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="27" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
@@ -1190,10 +1196,10 @@
         <v>35</v>
       </c>
       <c r="C30" s="12">
-        <v>47626</v>
+        <v>51013</v>
       </c>
       <c r="D30" s="12">
-        <v>51000</v>
+        <v>54000</v>
       </c>
       <c r="E30" s="3"/>
     </row>
@@ -1220,10 +1226,10 @@
         <v>37</v>
       </c>
       <c r="C32" s="5">
-        <v>23851</v>
+        <v>26836</v>
       </c>
       <c r="D32" s="5">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E32" s="3"/>
     </row>
@@ -1300,10 +1306,10 @@
         <v>42</v>
       </c>
       <c r="C37" s="12">
-        <v>42083</v>
+        <v>45126</v>
       </c>
       <c r="D37" s="12">
-        <v>45000</v>
+        <v>48000</v>
       </c>
       <c r="E37" s="3"/>
     </row>
@@ -1329,10 +1335,10 @@
         <v>44</v>
       </c>
       <c r="C39" s="5">
-        <v>12084</v>
+        <v>14654</v>
       </c>
       <c r="D39" s="5">
-        <v>15000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="27" x14ac:dyDescent="0.35">
@@ -1399,10 +1405,10 @@
         <v>49</v>
       </c>
       <c r="C44" s="5">
-        <v>6067</v>
+        <v>9031</v>
       </c>
       <c r="D44" s="5">
-        <v>9000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="27" x14ac:dyDescent="0.35">
@@ -1497,10 +1503,10 @@
         <v>56</v>
       </c>
       <c r="C51" s="5">
-        <v>1030</v>
+        <v>3011</v>
       </c>
       <c r="D51" s="5">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="27" x14ac:dyDescent="0.35">

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0CCB3A-20DE-6E47-B9E8-0CCA9D709C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FBEB34-EDE4-494E-B465-8770E6078E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1573,10 +1573,10 @@
         <v>49</v>
       </c>
       <c r="C44" s="17">
-        <v>18119</v>
+        <v>20929</v>
       </c>
       <c r="D44" s="17">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="E44" s="15"/>
       <c r="F44" s="21"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FBEB34-EDE4-494E-B465-8770E6078E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33ACC9AF-53D1-0545-B772-E4AAB567A845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="65">
   <si>
     <t>No.</t>
   </si>
@@ -1004,7 +1004,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="18">
-        <v>28988</v>
+        <v>38988</v>
       </c>
       <c r="D11" s="18">
         <v>42000</v>
@@ -1095,10 +1095,13 @@
         <v>13</v>
       </c>
       <c r="C17" s="17">
-        <v>27097</v>
+        <v>30014</v>
       </c>
       <c r="D17" s="17">
-        <v>30000</v>
+        <v>33000</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>64</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -1129,10 +1132,10 @@
         <v>22</v>
       </c>
       <c r="C19" s="17">
-        <v>29780</v>
+        <v>33042</v>
       </c>
       <c r="D19" s="17">
-        <v>33000</v>
+        <v>36000</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -1323,10 +1326,10 @@
         <v>35</v>
       </c>
       <c r="C30" s="17">
-        <v>17997</v>
+        <v>21039</v>
       </c>
       <c r="D30" s="17">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="E30" s="15"/>
       <c r="F30" s="21"/>
@@ -1447,10 +1450,10 @@
         <v>42</v>
       </c>
       <c r="C37" s="17">
-        <v>11991</v>
+        <v>14556</v>
       </c>
       <c r="D37" s="17">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="21"/>
@@ -1623,10 +1626,10 @@
         <v>55</v>
       </c>
       <c r="C47" s="17">
-        <v>3093</v>
+        <v>6112</v>
       </c>
       <c r="D47" s="17">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33ACC9AF-53D1-0545-B772-E4AAB567A845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B9D7E7-4284-8A48-BEC8-1879D55DD0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1272,10 +1272,10 @@
         <v>32</v>
       </c>
       <c r="C27" s="17">
-        <v>29279</v>
+        <v>32945</v>
       </c>
       <c r="D27" s="17">
-        <v>33000</v>
+        <v>36000</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="21"/>
@@ -1690,10 +1690,10 @@
         <v>60</v>
       </c>
       <c r="C51" s="17">
-        <v>3079</v>
+        <v>6057</v>
       </c>
       <c r="D51" s="17">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B9D7E7-4284-8A48-BEC8-1879D55DD0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1825B4A3-5C9B-5745-A76D-DA48255E902D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1396,10 +1396,10 @@
         <v>39</v>
       </c>
       <c r="C34" s="17">
-        <v>17912</v>
+        <v>21080</v>
       </c>
       <c r="D34" s="17">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="E34" s="15"/>
       <c r="F34" s="21"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1825B4A3-5C9B-5745-A76D-DA48255E902D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE00878-5384-B24A-BCF6-04DD47B07F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1308,10 +1308,10 @@
         <v>34</v>
       </c>
       <c r="C29" s="17">
-        <v>14927</v>
+        <v>17982</v>
       </c>
       <c r="D29" s="17">
-        <v>18000</v>
+        <v>21000</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="21"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE00878-5384-B24A-BCF6-04DD47B07F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36098707-0478-8F45-854D-DCF218821680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1254,10 +1254,10 @@
         <v>31</v>
       </c>
       <c r="C26" s="17">
-        <v>17985</v>
+        <v>20828</v>
       </c>
       <c r="D26" s="17">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="21"/>
@@ -1558,10 +1558,10 @@
         <v>48</v>
       </c>
       <c r="C43" s="17">
-        <v>21061</v>
+        <v>24116</v>
       </c>
       <c r="D43" s="17">
-        <v>24000</v>
+        <v>27000</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="21"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36098707-0478-8F45-854D-DCF218821680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7DE1D3-73BD-CD41-B04B-DE9D9A383473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -827,16 +827,18 @@
         <v>1</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" s="19">
-        <v>41904</v>
+        <v>51080</v>
       </c>
       <c r="D2" s="19">
-        <v>45000</v>
+        <v>54000</v>
       </c>
       <c r="E2" s="3"/>
-      <c r="F2" s="21"/>
+      <c r="F2" t="s">
+        <v>63</v>
+      </c>
       <c r="G2" s="6"/>
       <c r="H2" s="7" t="s">
         <v>6</v>
@@ -847,16 +849,18 @@
         <v>2</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C3" s="19">
-        <v>44680</v>
+        <v>50950</v>
       </c>
       <c r="D3" s="19">
-        <v>48000</v>
+        <v>53000</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="21"/>
+      <c r="F3" t="s">
+        <v>63</v>
+      </c>
       <c r="G3" s="8"/>
       <c r="H3" s="9" t="s">
         <v>50</v>
@@ -867,17 +871,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C4" s="19">
-        <v>51080</v>
+        <v>48003</v>
       </c>
       <c r="D4" s="19">
-        <v>54000</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" t="s">
-        <v>63</v>
+        <v>51000</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="11" t="s">
@@ -889,14 +889,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C5" s="19">
-        <v>48003</v>
+        <v>44680</v>
       </c>
       <c r="D5" s="19">
-        <v>51000</v>
-      </c>
+        <v>48000</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="21"/>
       <c r="G5" s="13"/>
       <c r="H5" s="7" t="s">
         <v>9</v>
@@ -907,17 +909,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C6" s="19">
-        <v>50950</v>
+        <v>41969</v>
       </c>
       <c r="D6" s="19">
-        <v>53000</v>
+        <v>45000</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" t="s">
-        <v>63</v>
+      <c r="F6" s="21" t="s">
+        <v>64</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -927,18 +929,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C7" s="19">
-        <v>41969</v>
+        <v>41904</v>
       </c>
       <c r="D7" s="19">
         <v>45000</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="21" t="s">
-        <v>64</v>
-      </c>
+      <c r="F7" s="21"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
@@ -946,13 +946,13 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="19">
-        <v>38901</v>
-      </c>
-      <c r="D8" s="19">
+      <c r="B8" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="18">
+        <v>39172</v>
+      </c>
+      <c r="D8" s="18">
         <v>42000</v>
       </c>
       <c r="E8" s="3"/>
@@ -964,17 +964,16 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>18</v>
+      <c r="B9" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="C9" s="18">
-        <v>36148</v>
+        <v>38988</v>
       </c>
       <c r="D9" s="18">
-        <v>39000</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="21"/>
+        <v>42000</v>
+      </c>
+      <c r="E9" s="12"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
@@ -983,10 +982,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C10" s="18">
-        <v>39172</v>
+        <v>38901</v>
       </c>
       <c r="D10" s="18">
         <v>42000</v>
@@ -1000,16 +999,17 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="18" t="s">
-        <v>20</v>
+      <c r="B11" s="20" t="s">
+        <v>18</v>
       </c>
       <c r="C11" s="18">
-        <v>38988</v>
+        <v>36148</v>
       </c>
       <c r="D11" s="18">
-        <v>42000</v>
-      </c>
-      <c r="E11" s="12"/>
+        <v>39000</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="21"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
@@ -1018,42 +1018,43 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C12" s="17">
-        <v>14866</v>
+        <v>33062</v>
       </c>
       <c r="D12" s="17">
-        <v>18000</v>
-      </c>
+        <v>36000</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="21"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C13" s="17">
-        <v>12047</v>
+        <v>33042</v>
       </c>
       <c r="D13" s="17">
-        <v>15000</v>
-      </c>
-      <c r="E13" s="3"/>
+        <v>36000</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C14" s="17">
-        <v>14916</v>
+        <v>32993</v>
       </c>
       <c r="D14" s="17">
-        <v>18000</v>
+        <v>36000</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="21"/>
@@ -1063,28 +1064,32 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C15" s="17">
-        <v>17822</v>
+        <v>32945</v>
       </c>
       <c r="D15" s="17">
-        <v>21000</v>
-      </c>
-      <c r="E15" s="3"/>
+        <v>36000</v>
+      </c>
+      <c r="E15" s="15"/>
+      <c r="F15" s="21"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" s="17">
-        <v>21012</v>
+        <v>30014</v>
       </c>
       <c r="D16" s="17">
-        <v>24000</v>
+        <v>33000</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -1092,17 +1097,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C17" s="17">
-        <v>30014</v>
+        <v>29918</v>
       </c>
       <c r="D17" s="17">
         <v>33000</v>
       </c>
-      <c r="F17" s="21" t="s">
-        <v>64</v>
-      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="21"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
@@ -1129,14 +1133,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C19" s="17">
-        <v>33042</v>
+        <v>24116</v>
       </c>
       <c r="D19" s="17">
-        <v>36000</v>
-      </c>
+        <v>27000</v>
+      </c>
+      <c r="E19" s="15"/>
+      <c r="F19" s="21"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
@@ -1145,14 +1151,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C20" s="17">
-        <v>20985</v>
+        <v>21080</v>
       </c>
       <c r="D20" s="17">
         <v>24000</v>
       </c>
+      <c r="E20" s="15"/>
+      <c r="F20" s="21"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
@@ -1161,15 +1169,15 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C21" s="17">
-        <v>14692</v>
+        <v>21039</v>
       </c>
       <c r="D21" s="17">
-        <v>18000</v>
-      </c>
-      <c r="E21" s="3"/>
+        <v>24000</v>
+      </c>
+      <c r="E21" s="15"/>
       <c r="F21" s="21"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
@@ -1179,15 +1187,15 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C22" s="17">
-        <v>14758</v>
+        <v>21020</v>
       </c>
       <c r="D22" s="17">
-        <v>18000</v>
-      </c>
-      <c r="E22" s="3"/>
+        <v>24000</v>
+      </c>
+      <c r="E22" s="15"/>
       <c r="F22" s="21"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -1197,16 +1205,14 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C23" s="17">
-        <v>29847</v>
+        <v>21012</v>
       </c>
       <c r="D23" s="17">
-        <v>33000</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="21"/>
+        <v>24000</v>
+      </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
@@ -1215,16 +1221,14 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C24" s="17">
-        <v>32993</v>
+        <v>20985</v>
       </c>
       <c r="D24" s="17">
-        <v>36000</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="21"/>
+        <v>24000</v>
+      </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
@@ -1233,15 +1237,15 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="C25" s="17">
-        <v>29918</v>
+        <v>20929</v>
       </c>
       <c r="D25" s="17">
-        <v>33000</v>
-      </c>
-      <c r="E25" s="3"/>
+        <v>24000</v>
+      </c>
+      <c r="E25" s="15"/>
       <c r="F25" s="21"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
@@ -1269,13 +1273,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C27" s="17">
-        <v>32945</v>
+        <v>18101</v>
       </c>
       <c r="D27" s="17">
-        <v>36000</v>
+        <v>21000</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="21"/>
@@ -1287,13 +1291,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C28" s="17">
-        <v>14830</v>
+        <v>18033</v>
       </c>
       <c r="D28" s="17">
-        <v>18000</v>
+        <v>21000</v>
       </c>
       <c r="E28" s="15"/>
       <c r="F28" s="21"/>
@@ -1323,31 +1327,30 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C30" s="17">
-        <v>21039</v>
+        <v>17822</v>
       </c>
       <c r="D30" s="17">
-        <v>24000</v>
-      </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="21"/>
+        <v>21000</v>
+      </c>
+      <c r="E30" s="3"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C31" s="17">
-        <v>3024</v>
+        <v>14916</v>
       </c>
       <c r="D31" s="17">
-        <v>6000</v>
-      </c>
-      <c r="E31" s="15"/>
+        <v>18000</v>
+      </c>
+      <c r="E31" s="3"/>
       <c r="F31" s="21"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -1357,16 +1360,14 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="C32" s="17">
-        <v>18033</v>
+        <v>14866</v>
       </c>
       <c r="D32" s="17">
-        <v>21000</v>
-      </c>
-      <c r="E32" s="15"/>
-      <c r="F32" s="21"/>
+        <v>18000</v>
+      </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
@@ -1375,13 +1376,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C33" s="17">
-        <v>8986</v>
+        <v>14830</v>
       </c>
       <c r="D33" s="17">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="21"/>
@@ -1393,13 +1394,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C34" s="17">
-        <v>21080</v>
+        <v>14793</v>
       </c>
       <c r="D34" s="17">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="E34" s="15"/>
       <c r="F34" s="21"/>
@@ -1411,15 +1412,15 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C35" s="17">
-        <v>8659</v>
+        <v>14758</v>
       </c>
       <c r="D35" s="17">
-        <v>12000</v>
-      </c>
-      <c r="E35" s="15"/>
+        <v>18000</v>
+      </c>
+      <c r="E35" s="3"/>
       <c r="F35" s="21"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -1429,15 +1430,15 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C36" s="17">
-        <v>18101</v>
+        <v>14692</v>
       </c>
       <c r="D36" s="17">
-        <v>21000</v>
-      </c>
-      <c r="E36" s="15"/>
+        <v>18000</v>
+      </c>
+      <c r="E36" s="3"/>
       <c r="F36" s="21"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
@@ -1465,13 +1466,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C38" s="17">
-        <v>21020</v>
+        <v>14527</v>
       </c>
       <c r="D38" s="17">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="E38" s="15"/>
       <c r="F38" s="21"/>
@@ -1501,16 +1502,15 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="C40" s="17">
-        <v>14793</v>
+        <v>12047</v>
       </c>
       <c r="D40" s="17">
-        <v>18000</v>
-      </c>
-      <c r="E40" s="15"/>
-      <c r="F40" s="21"/>
+        <v>15000</v>
+      </c>
+      <c r="E40" s="3"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
@@ -1519,10 +1519,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C41" s="17">
-        <v>8433</v>
+        <v>8986</v>
       </c>
       <c r="D41" s="17">
         <v>12000</v>
@@ -1537,13 +1537,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C42" s="17">
-        <v>14527</v>
+        <v>8659</v>
       </c>
       <c r="D42" s="17">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="E42" s="15"/>
       <c r="F42" s="21"/>
@@ -1555,13 +1555,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C43" s="17">
-        <v>24116</v>
+        <v>8433</v>
       </c>
       <c r="D43" s="17">
-        <v>27000</v>
+        <v>12000</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="21"/>
@@ -1573,16 +1573,14 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C44" s="17">
-        <v>20929</v>
+        <v>6112</v>
       </c>
       <c r="D44" s="17">
-        <v>24000</v>
-      </c>
-      <c r="E44" s="15"/>
-      <c r="F44" s="21"/>
+        <v>9000</v>
+      </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
     </row>
@@ -1591,13 +1589,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C45" s="17">
-        <v>3136</v>
+        <v>6057</v>
       </c>
       <c r="D45" s="17">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -1607,13 +1605,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C46" s="17">
-        <v>2954</v>
+        <v>6025</v>
       </c>
       <c r="D46" s="17">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -1623,13 +1621,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C47" s="17">
-        <v>6112</v>
+        <v>3136</v>
       </c>
       <c r="D47" s="17">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -1639,14 +1637,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C48" s="17">
-        <v>975</v>
+        <v>3024</v>
       </c>
       <c r="D48" s="17">
-        <v>3000</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="E48" s="15"/>
+      <c r="F48" s="21"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
     </row>
@@ -1671,13 +1671,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C50" s="17">
-        <v>6025</v>
+        <v>2954</v>
       </c>
       <c r="D50" s="17">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -1687,13 +1687,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C51" s="17">
-        <v>6057</v>
+        <v>1005</v>
       </c>
       <c r="D51" s="17">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -1702,14 +1702,20 @@
       <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C52" s="17">
-        <v>1005</v>
-      </c>
-      <c r="D52" s="17">
+      <c r="B52" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52" s="24">
+        <v>982</v>
+      </c>
+      <c r="D52" s="24">
         <v>3000</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F52" s="22" t="s">
+        <v>62</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -1718,20 +1724,14 @@
       <c r="A53" s="2">
         <v>52</v>
       </c>
-      <c r="B53" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="C53" s="24">
-        <v>982</v>
-      </c>
-      <c r="D53" s="24">
+      <c r="B53" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="17">
+        <v>975</v>
+      </c>
+      <c r="D53" s="17">
         <v>3000</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F53" s="22" t="s">
-        <v>62</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -1741,6 +1741,9 @@
     <row r="72" x14ac:dyDescent="0.35"/>
     <row r="73" x14ac:dyDescent="0.35"/>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F73">
+    <sortCondition descending="1" ref="D1:D74"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7DE1D3-73BD-CD41-B04B-DE9D9A383473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B68417-11A1-1644-AE99-85BE21D2B602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1342,15 +1342,15 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C31" s="17">
-        <v>14916</v>
+        <v>18083</v>
       </c>
       <c r="D31" s="17">
-        <v>18000</v>
-      </c>
-      <c r="E31" s="3"/>
+        <v>21000</v>
+      </c>
+      <c r="E31" s="15"/>
       <c r="F31" s="21"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -1360,14 +1360,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C32" s="17">
-        <v>14866</v>
+        <v>14916</v>
       </c>
       <c r="D32" s="17">
         <v>18000</v>
       </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="21"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
@@ -1376,16 +1378,14 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="C33" s="17">
-        <v>14830</v>
+        <v>14866</v>
       </c>
       <c r="D33" s="17">
         <v>18000</v>
       </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="21"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
@@ -1394,10 +1394,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C34" s="17">
-        <v>14793</v>
+        <v>14830</v>
       </c>
       <c r="D34" s="17">
         <v>18000</v>
@@ -1742,7 +1742,7 @@
     <row r="73" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F73">
-    <sortCondition descending="1" ref="D1:D74"/>
+    <sortCondition descending="1" ref="D1:D73"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B68417-11A1-1644-AE99-85BE21D2B602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4B33E6-36B2-2448-8E4D-5C7ED6C0E9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1573,13 +1573,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C44" s="17">
-        <v>6112</v>
+        <v>8847</v>
       </c>
       <c r="D44" s="17">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -1589,10 +1589,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C45" s="17">
-        <v>6057</v>
+        <v>6112</v>
       </c>
       <c r="D45" s="17">
         <v>9000</v>
@@ -1605,10 +1605,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C46" s="17">
-        <v>6025</v>
+        <v>6057</v>
       </c>
       <c r="D46" s="17">
         <v>9000</v>
@@ -1621,13 +1621,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C47" s="17">
-        <v>3136</v>
+        <v>6025</v>
       </c>
       <c r="D47" s="17">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -1637,16 +1637,14 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C48" s="17">
-        <v>3024</v>
+        <v>3136</v>
       </c>
       <c r="D48" s="17">
         <v>6000</v>
       </c>
-      <c r="E48" s="15"/>
-      <c r="F48" s="21"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
     </row>
@@ -1655,14 +1653,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C49" s="17">
-        <v>3020</v>
+        <v>3024</v>
       </c>
       <c r="D49" s="17">
         <v>6000</v>
       </c>
+      <c r="E49" s="15"/>
+      <c r="F49" s="21"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4B33E6-36B2-2448-8E4D-5C7ED6C0E9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB516C90-FE87-6B4E-9925-1B762AAD9239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -830,10 +830,10 @@
         <v>14</v>
       </c>
       <c r="C2" s="19">
-        <v>51080</v>
+        <v>54008</v>
       </c>
       <c r="D2" s="19">
-        <v>54000</v>
+        <v>57000</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" t="s">

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB516C90-FE87-6B4E-9925-1B762AAD9239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD22EAA-090E-DF4D-958B-4C3BD6C974AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -950,10 +950,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="18">
-        <v>39172</v>
+        <v>42086</v>
       </c>
       <c r="D8" s="18">
-        <v>42000</v>
+        <v>45000</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="21"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD22EAA-090E-DF4D-958B-4C3BD6C974AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8C3DB9-60F4-1440-BBB5-3304F394A49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -383,7 +383,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -453,6 +453,7 @@
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -946,13 +947,13 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <v>42086</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="19">
         <v>45000</v>
       </c>
       <c r="E8" s="3"/>
@@ -964,7 +965,7 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="25" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="18">
@@ -1151,16 +1152,14 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C20" s="17">
-        <v>21080</v>
+        <v>23903</v>
       </c>
       <c r="D20" s="17">
-        <v>24000</v>
-      </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="21"/>
+        <v>27000</v>
+      </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
@@ -1169,10 +1168,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C21" s="17">
-        <v>21039</v>
+        <v>21080</v>
       </c>
       <c r="D21" s="17">
         <v>24000</v>
@@ -1187,10 +1186,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C22" s="17">
-        <v>21020</v>
+        <v>21039</v>
       </c>
       <c r="D22" s="17">
         <v>24000</v>
@@ -1205,14 +1204,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="C23" s="17">
-        <v>21012</v>
+        <v>21020</v>
       </c>
       <c r="D23" s="17">
         <v>24000</v>
       </c>
+      <c r="E23" s="15"/>
+      <c r="F23" s="21"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
@@ -1276,10 +1277,10 @@
         <v>41</v>
       </c>
       <c r="C27" s="17">
-        <v>18101</v>
+        <v>20642</v>
       </c>
       <c r="D27" s="17">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="21"/>
@@ -1360,15 +1361,15 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C32" s="17">
-        <v>14916</v>
+        <v>17763</v>
       </c>
       <c r="D32" s="17">
-        <v>18000</v>
-      </c>
-      <c r="E32" s="3"/>
+        <v>21000</v>
+      </c>
+      <c r="E32" s="15"/>
       <c r="F32" s="21"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -1378,14 +1379,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C33" s="17">
-        <v>14866</v>
+        <v>14916</v>
       </c>
       <c r="D33" s="17">
         <v>18000</v>
       </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="21"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
@@ -1394,16 +1397,14 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="C34" s="17">
-        <v>14830</v>
+        <v>14866</v>
       </c>
       <c r="D34" s="17">
         <v>18000</v>
       </c>
-      <c r="E34" s="15"/>
-      <c r="F34" s="21"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
@@ -1522,10 +1523,10 @@
         <v>38</v>
       </c>
       <c r="C41" s="17">
-        <v>8986</v>
+        <v>11999</v>
       </c>
       <c r="D41" s="17">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="21"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8C3DB9-60F4-1440-BBB5-3304F394A49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FA45C1-6480-F14C-86EA-A1D078E62C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1081,33 +1081,33 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C16" s="17">
-        <v>30014</v>
+        <v>33004</v>
       </c>
       <c r="D16" s="17">
-        <v>33000</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>64</v>
-      </c>
+        <v>36000</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="21"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" s="17">
-        <v>29918</v>
+        <v>30014</v>
       </c>
       <c r="D17" s="17">
         <v>33000</v>
       </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="21"/>
+      <c r="F17" s="21" t="s">
+        <v>64</v>
+      </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
@@ -1292,16 +1292,14 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="C28" s="17">
-        <v>18033</v>
+        <v>20909</v>
       </c>
       <c r="D28" s="17">
-        <v>21000</v>
-      </c>
-      <c r="E28" s="15"/>
-      <c r="F28" s="21"/>
+        <v>24000</v>
+      </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
@@ -1310,10 +1308,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C29" s="17">
-        <v>17982</v>
+        <v>18033</v>
       </c>
       <c r="D29" s="17">
         <v>21000</v>
@@ -1328,31 +1326,31 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C30" s="17">
-        <v>17822</v>
+        <v>17982</v>
       </c>
       <c r="D30" s="17">
         <v>21000</v>
       </c>
-      <c r="E30" s="3"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="21"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="C31" s="17">
-        <v>18083</v>
+        <v>17822</v>
       </c>
       <c r="D31" s="17">
         <v>21000</v>
       </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="21"/>
+      <c r="E31" s="3"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
@@ -1361,10 +1359,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C32" s="17">
-        <v>17763</v>
+        <v>18083</v>
       </c>
       <c r="D32" s="17">
         <v>21000</v>
@@ -1379,15 +1377,15 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C33" s="17">
-        <v>14916</v>
+        <v>17763</v>
       </c>
       <c r="D33" s="17">
-        <v>18000</v>
-      </c>
-      <c r="E33" s="3"/>
+        <v>21000</v>
+      </c>
+      <c r="E33" s="15"/>
       <c r="F33" s="21"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
@@ -1397,14 +1395,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C34" s="17">
-        <v>14866</v>
+        <v>14916</v>
       </c>
       <c r="D34" s="17">
         <v>18000</v>
       </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="21"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FA45C1-6480-F14C-86EA-A1D078E62C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9D7000-2A0B-1F40-B107-A562A64D8157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1398,10 +1398,10 @@
         <v>10</v>
       </c>
       <c r="C34" s="17">
-        <v>14916</v>
+        <v>17866</v>
       </c>
       <c r="D34" s="17">
-        <v>18000</v>
+        <v>21000</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="21"/>
@@ -1488,10 +1488,10 @@
         <v>44</v>
       </c>
       <c r="C39" s="17">
-        <v>12126</v>
+        <v>15013</v>
       </c>
       <c r="D39" s="17">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="21"/>
@@ -1590,13 +1590,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C45" s="17">
-        <v>6112</v>
+        <v>8677</v>
       </c>
       <c r="D45" s="17">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -1606,13 +1606,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C46" s="17">
-        <v>6057</v>
+        <v>9122</v>
       </c>
       <c r="D46" s="17">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -1622,10 +1622,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C47" s="17">
-        <v>6025</v>
+        <v>6112</v>
       </c>
       <c r="D47" s="17">
         <v>9000</v>
@@ -1638,13 +1638,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C48" s="17">
-        <v>3136</v>
+        <v>6057</v>
       </c>
       <c r="D48" s="17">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9D7000-2A0B-1F40-B107-A562A64D8157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DF8BF4-FE17-D847-9368-C486463CC3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -910,18 +910,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C6" s="19">
-        <v>41969</v>
+        <v>45019</v>
       </c>
       <c r="D6" s="19">
-        <v>45000</v>
+        <v>48000</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="21" t="s">
-        <v>64</v>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
@@ -930,16 +928,18 @@
         <v>6</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C7" s="19">
-        <v>41904</v>
+        <v>41969</v>
       </c>
       <c r="D7" s="19">
         <v>45000</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="21"/>
+      <c r="F7" s="21" t="s">
+        <v>64</v>
+      </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
@@ -1168,13 +1168,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C21" s="17">
-        <v>21080</v>
+        <v>23978</v>
       </c>
       <c r="D21" s="17">
-        <v>24000</v>
+        <v>27000</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="21"/>
@@ -1186,10 +1186,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C22" s="17">
-        <v>21039</v>
+        <v>21080</v>
       </c>
       <c r="D22" s="17">
         <v>24000</v>
@@ -1204,10 +1204,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C23" s="17">
-        <v>21020</v>
+        <v>21039</v>
       </c>
       <c r="D23" s="17">
         <v>24000</v>
@@ -1222,14 +1222,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C24" s="17">
-        <v>20985</v>
+        <v>21020</v>
       </c>
       <c r="D24" s="17">
         <v>24000</v>
       </c>
+      <c r="E24" s="15"/>
+      <c r="F24" s="21"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
@@ -1238,16 +1240,14 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="C25" s="17">
-        <v>20929</v>
+        <v>20985</v>
       </c>
       <c r="D25" s="17">
         <v>24000</v>
       </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="21"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
@@ -1691,10 +1691,10 @@
         <v>61</v>
       </c>
       <c r="C51" s="17">
-        <v>1005</v>
+        <v>2979</v>
       </c>
       <c r="D51" s="17">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DF8BF4-FE17-D847-9368-C486463CC3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9AC38E-1C39-004F-B27D-A8ECDD9E2495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1506,10 +1506,10 @@
         <v>8</v>
       </c>
       <c r="C40" s="17">
-        <v>12047</v>
+        <v>14948</v>
       </c>
       <c r="D40" s="17">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="E40" s="3"/>
       <c r="G40" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9AC38E-1C39-004F-B27D-A8ECDD9E2495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CC26EB-E1B5-0A45-8C03-B0AA77D7352A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1003,7 +1003,7 @@
       <c r="B11" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="20">
         <v>36148</v>
       </c>
       <c r="D11" s="18">
@@ -1018,14 +1018,14 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="17">
-        <v>33062</v>
-      </c>
-      <c r="D12" s="17">
-        <v>36000</v>
+      <c r="B12" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="20">
+        <v>36024</v>
+      </c>
+      <c r="D12" s="18">
+        <v>39000</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="21"/>
@@ -1035,30 +1035,30 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C13" s="17">
-        <v>33042</v>
+        <v>33062</v>
       </c>
       <c r="D13" s="17">
         <v>36000</v>
       </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C14" s="17">
-        <v>32993</v>
+        <v>33042</v>
       </c>
       <c r="D14" s="17">
         <v>36000</v>
       </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="21"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
@@ -1207,10 +1207,10 @@
         <v>35</v>
       </c>
       <c r="C23" s="17">
-        <v>21039</v>
+        <v>23999</v>
       </c>
       <c r="D23" s="17">
-        <v>24000</v>
+        <v>27000</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="21"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CC26EB-E1B5-0A45-8C03-B0AA77D7352A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A623276-EC06-E646-B390-400FCD2269BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1001,10 +1001,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C11" s="20">
-        <v>36148</v>
+        <v>36024</v>
       </c>
       <c r="D11" s="18">
         <v>39000</v>
@@ -1019,10 +1019,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C12" s="20">
-        <v>36024</v>
+        <v>36148</v>
       </c>
       <c r="D12" s="18">
         <v>39000</v>
@@ -1035,45 +1035,45 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C13" s="17">
-        <v>33062</v>
+        <v>33042</v>
       </c>
       <c r="D13" s="17">
         <v>36000</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C14" s="17">
-        <v>33042</v>
+        <v>33062</v>
       </c>
       <c r="D14" s="17">
         <v>36000</v>
       </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="21"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C15" s="17">
-        <v>32945</v>
+        <v>33004</v>
       </c>
       <c r="D15" s="17">
         <v>36000</v>
       </c>
-      <c r="E15" s="15"/>
+      <c r="E15" s="3"/>
       <c r="F15" s="21"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -1081,15 +1081,15 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C16" s="17">
-        <v>33004</v>
+        <v>32945</v>
       </c>
       <c r="D16" s="17">
         <v>36000</v>
       </c>
-      <c r="E16" s="3"/>
+      <c r="E16" s="15"/>
       <c r="F16" s="21"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -1097,17 +1097,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C17" s="17">
-        <v>30014</v>
+        <v>29439</v>
       </c>
       <c r="D17" s="17">
         <v>33000</v>
       </c>
-      <c r="F17" s="21" t="s">
-        <v>64</v>
-      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="21"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
@@ -1116,16 +1115,17 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C18" s="17">
-        <v>29439</v>
+        <v>30014</v>
       </c>
       <c r="D18" s="17">
         <v>33000</v>
       </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="21"/>
+      <c r="F18" s="21" t="s">
+        <v>64</v>
+      </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
@@ -1134,16 +1134,14 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C19" s="17">
-        <v>24116</v>
+        <v>23903</v>
       </c>
       <c r="D19" s="17">
         <v>27000</v>
       </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="21"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
@@ -1152,14 +1150,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C20" s="17">
-        <v>23903</v>
+        <v>23931</v>
       </c>
       <c r="D20" s="17">
         <v>27000</v>
       </c>
+      <c r="E20" s="15"/>
+      <c r="F20" s="21"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
@@ -1168,10 +1168,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C21" s="17">
-        <v>23978</v>
+        <v>23999</v>
       </c>
       <c r="D21" s="17">
         <v>27000</v>
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C22" s="17">
-        <v>21080</v>
+        <v>24116</v>
       </c>
       <c r="D22" s="17">
-        <v>24000</v>
+        <v>27000</v>
       </c>
       <c r="E22" s="15"/>
       <c r="F22" s="21"/>
@@ -1204,10 +1204,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C23" s="17">
-        <v>23999</v>
+        <v>23978</v>
       </c>
       <c r="D23" s="17">
         <v>27000</v>
@@ -1222,16 +1222,14 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C24" s="17">
-        <v>21020</v>
+        <v>20985</v>
       </c>
       <c r="D24" s="17">
         <v>24000</v>
       </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="21"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
@@ -1240,10 +1238,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C25" s="17">
-        <v>20985</v>
+        <v>20909</v>
       </c>
       <c r="D25" s="17">
         <v>24000</v>
@@ -1256,10 +1254,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C26" s="17">
-        <v>20828</v>
+        <v>20642</v>
       </c>
       <c r="D26" s="17">
         <v>24000</v>
@@ -1274,10 +1272,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C27" s="17">
-        <v>20642</v>
+        <v>21020</v>
       </c>
       <c r="D27" s="17">
         <v>24000</v>
@@ -1292,14 +1290,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C28" s="17">
-        <v>20909</v>
+        <v>21080</v>
       </c>
       <c r="D28" s="17">
         <v>24000</v>
       </c>
+      <c r="E28" s="15"/>
+      <c r="F28" s="21"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
@@ -1308,15 +1308,15 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C29" s="17">
-        <v>18033</v>
+        <v>17866</v>
       </c>
       <c r="D29" s="17">
         <v>21000</v>
       </c>
-      <c r="E29" s="15"/>
+      <c r="E29" s="3"/>
       <c r="F29" s="21"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
@@ -1326,31 +1326,31 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C30" s="17">
-        <v>17982</v>
+        <v>17822</v>
       </c>
       <c r="D30" s="17">
         <v>21000</v>
       </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="21"/>
+      <c r="E30" s="3"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C31" s="17">
-        <v>17822</v>
+        <v>17982</v>
       </c>
       <c r="D31" s="17">
         <v>21000</v>
       </c>
-      <c r="E31" s="3"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="21"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
@@ -1359,10 +1359,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C32" s="17">
-        <v>18083</v>
+        <v>18033</v>
       </c>
       <c r="D32" s="17">
         <v>21000</v>
@@ -1395,15 +1395,15 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C34" s="17">
-        <v>17866</v>
+        <v>18083</v>
       </c>
       <c r="D34" s="17">
         <v>21000</v>
       </c>
-      <c r="E34" s="3"/>
+      <c r="E34" s="15"/>
       <c r="F34" s="21"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
@@ -1449,16 +1449,15 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="C37" s="17">
-        <v>14556</v>
+        <v>14948</v>
       </c>
       <c r="D37" s="17">
         <v>18000</v>
       </c>
-      <c r="E37" s="15"/>
-      <c r="F37" s="21"/>
+      <c r="E37" s="3"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
@@ -1467,10 +1466,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C38" s="17">
-        <v>14527</v>
+        <v>14556</v>
       </c>
       <c r="D38" s="17">
         <v>18000</v>
@@ -1503,15 +1502,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C40" s="17">
-        <v>14948</v>
+        <v>14527</v>
       </c>
       <c r="D40" s="17">
         <v>18000</v>
       </c>
-      <c r="E40" s="3"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="21"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
@@ -1574,10 +1574,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C44" s="17">
-        <v>8847</v>
+        <v>9122</v>
       </c>
       <c r="D44" s="17">
         <v>12000</v>
@@ -1590,10 +1590,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C45" s="17">
-        <v>8677</v>
+        <v>8847</v>
       </c>
       <c r="D45" s="17">
         <v>12000</v>
@@ -1606,10 +1606,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C46" s="17">
-        <v>9122</v>
+        <v>8677</v>
       </c>
       <c r="D46" s="17">
         <v>12000</v>
@@ -1672,10 +1672,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C50" s="17">
-        <v>2954</v>
+        <v>2979</v>
       </c>
       <c r="D50" s="17">
         <v>6000</v>
@@ -1688,10 +1688,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C51" s="17">
-        <v>2979</v>
+        <v>2954</v>
       </c>
       <c r="D51" s="17">
         <v>6000</v>
@@ -1703,20 +1703,14 @@
       <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="B52" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="C52" s="24">
-        <v>982</v>
-      </c>
-      <c r="D52" s="24">
+      <c r="B52" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="17">
+        <v>975</v>
+      </c>
+      <c r="D52" s="17">
         <v>3000</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F52" s="22" t="s">
-        <v>62</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -1725,14 +1719,20 @@
       <c r="A53" s="2">
         <v>52</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C53" s="17">
-        <v>975</v>
-      </c>
-      <c r="D53" s="17">
+      <c r="B53" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" s="24">
+        <v>982</v>
+      </c>
+      <c r="D53" s="24">
         <v>3000</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F53" s="22" t="s">
+        <v>62</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -1743,7 +1743,7 @@
     <row r="73" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F73">
-    <sortCondition descending="1" ref="D1:D73"/>
+    <sortCondition descending="1" ref="D1:D74"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A623276-EC06-E646-B390-400FCD2269BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB224E50-4109-9D4B-B4E6-503B5FAA51A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1622,13 +1622,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C47" s="17">
-        <v>6112</v>
+        <v>9094</v>
       </c>
       <c r="D47" s="17">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -1638,10 +1638,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C48" s="17">
-        <v>6057</v>
+        <v>6112</v>
       </c>
       <c r="D48" s="17">
         <v>9000</v>
@@ -1743,7 +1743,7 @@
     <row r="73" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F73">
-    <sortCondition descending="1" ref="D1:D74"/>
+    <sortCondition descending="1" ref="D1:D73"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB224E50-4109-9D4B-B4E6-503B5FAA51A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBC5D0D-AD60-1445-A0C0-C85EF1528BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25520" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
   <sheets>
     <sheet name="Fleet Mileage" sheetId="1" r:id="rId1"/>
@@ -187,9 +187,6 @@
     <t>MK81DTGP</t>
   </si>
   <si>
-    <t>Vehicle is still in the fleet and approaching high mileage</t>
-  </si>
-  <si>
     <t>Recommended for Retirement</t>
   </si>
   <si>
@@ -230,6 +227,9 @@
   </si>
   <si>
     <t xml:space="preserve">Steering Stem was never replaced during accident repair. </t>
+  </si>
+  <si>
+    <t>Vehicle approaching high mileage</t>
   </si>
 </sst>
 </file>
@@ -355,7 +355,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -378,12 +378,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -398,30 +409,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -432,9 +422,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -453,7 +440,30 @@
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -793,13 +803,13 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.1640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="60.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" customWidth="1"/>
-    <col min="8" max="8" width="83.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="51" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="10.83203125" hidden="1"/>
   </cols>
   <sheetData>
@@ -810,38 +820,38 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="3" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="11">
         <v>54008</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="11">
         <v>57000</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="17"/>
+      <c r="H2" s="18" t="s">
         <v>6</v>
       </c>
     </row>
@@ -849,59 +859,59 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="11">
         <v>50950</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="11">
         <v>53000</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="9" t="s">
-        <v>50</v>
+        <v>62</v>
+      </c>
+      <c r="G3" s="19"/>
+      <c r="H3" s="20" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="11">
         <v>48003</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="11">
         <v>51000</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="11" t="s">
-        <v>51</v>
+      <c r="G4" s="21"/>
+      <c r="H4" s="22" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="11">
         <v>44680</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="11">
         <v>48000</v>
       </c>
       <c r="E5" s="3"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="7" t="s">
+      <c r="F5" s="13"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="18" t="s">
         <v>9</v>
       </c>
     </row>
@@ -909,17 +919,17 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="11">
         <v>45019</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="11">
         <v>48000</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="21"/>
+      <c r="F6" s="13"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
@@ -927,18 +937,18 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="11">
         <v>41969</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="11">
         <v>45000</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="21" t="s">
-        <v>64</v>
+      <c r="F7" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -947,150 +957,150 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="11">
         <v>42086</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="11">
         <v>45000</v>
       </c>
       <c r="E8" s="3"/>
-      <c r="F8" s="21"/>
+      <c r="F8" s="13"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="12">
         <v>38988</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="12">
         <v>42000</v>
       </c>
-      <c r="E9" s="12"/>
+      <c r="E9" s="6"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="12">
         <v>38901</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="12">
         <v>42000</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10" s="21"/>
+      <c r="F10" s="13"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="12">
         <v>36024</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="12">
         <v>39000</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="21"/>
+      <c r="F11" s="13"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="12">
         <v>36148</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="12">
         <v>39000</v>
       </c>
       <c r="E12" s="3"/>
-      <c r="F12" s="21"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="17">
-        <v>33042</v>
-      </c>
-      <c r="D13" s="17">
-        <v>36000</v>
-      </c>
+      <c r="B13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="12">
+        <v>36107</v>
+      </c>
+      <c r="D13" s="12">
+        <v>39000</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="17">
-        <v>33062</v>
-      </c>
-      <c r="D14" s="17">
+        <v>22</v>
+      </c>
+      <c r="C14" s="10">
+        <v>33042</v>
+      </c>
+      <c r="D14" s="10">
         <v>36000</v>
       </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="21"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="17">
-        <v>33004</v>
-      </c>
-      <c r="D15" s="17">
+        <v>27</v>
+      </c>
+      <c r="C15" s="10">
+        <v>33062</v>
+      </c>
+      <c r="D15" s="10">
         <v>36000</v>
       </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="21"/>
+      <c r="F15" s="13"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="17">
-        <v>32945</v>
-      </c>
-      <c r="D16" s="17">
+        <v>15</v>
+      </c>
+      <c r="C16" s="10">
+        <v>33004</v>
+      </c>
+      <c r="D16" s="10">
         <v>36000</v>
       </c>
-      <c r="E16" s="15"/>
-      <c r="F16" s="21"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="13"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
@@ -1099,14 +1109,14 @@
       <c r="B17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="10">
         <v>29439</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="10">
         <v>33000</v>
       </c>
       <c r="E17" s="3"/>
-      <c r="F17" s="21"/>
+      <c r="F17" s="13"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
@@ -1117,14 +1127,14 @@
       <c r="B18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="10">
         <v>30014</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="10">
         <v>33000</v>
       </c>
-      <c r="F18" s="21" t="s">
-        <v>64</v>
+      <c r="F18" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -1134,14 +1144,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="17">
-        <v>23903</v>
-      </c>
-      <c r="D19" s="17">
-        <v>27000</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C19" s="10">
+        <v>27165</v>
+      </c>
+      <c r="D19" s="10">
+        <v>30000</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="13"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
@@ -1150,16 +1162,14 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="17">
-        <v>23931</v>
-      </c>
-      <c r="D20" s="17">
+        <v>12</v>
+      </c>
+      <c r="C20" s="10">
+        <v>23903</v>
+      </c>
+      <c r="D20" s="10">
         <v>27000</v>
       </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="21"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
@@ -1168,16 +1178,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="17">
-        <v>23999</v>
-      </c>
-      <c r="D21" s="17">
+        <v>31</v>
+      </c>
+      <c r="C21" s="10">
+        <v>23931</v>
+      </c>
+      <c r="D21" s="10">
         <v>27000</v>
       </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="21"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="13"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
@@ -1186,16 +1196,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="17">
-        <v>24116</v>
-      </c>
-      <c r="D22" s="17">
+        <v>35</v>
+      </c>
+      <c r="C22" s="10">
+        <v>23999</v>
+      </c>
+      <c r="D22" s="10">
         <v>27000</v>
       </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="21"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="13"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
@@ -1206,14 +1216,14 @@
       <c r="B23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="10">
         <v>23978</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="10">
         <v>27000</v>
       </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="21"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="13"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
@@ -1222,14 +1232,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="17">
-        <v>20985</v>
-      </c>
-      <c r="D24" s="17">
-        <v>24000</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="C24" s="10">
+        <v>24261</v>
+      </c>
+      <c r="D24" s="10">
+        <v>27000</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="13"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
@@ -1238,12 +1250,12 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="17">
-        <v>20909</v>
-      </c>
-      <c r="D25" s="17">
+        <v>17</v>
+      </c>
+      <c r="C25" s="10">
+        <v>20985</v>
+      </c>
+      <c r="D25" s="10">
         <v>24000</v>
       </c>
       <c r="G25" s="4"/>
@@ -1254,16 +1266,14 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="17">
-        <v>20642</v>
-      </c>
-      <c r="D26" s="17">
+        <v>5</v>
+      </c>
+      <c r="C26" s="10">
+        <v>20909</v>
+      </c>
+      <c r="D26" s="10">
         <v>24000</v>
       </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="21"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
@@ -1272,16 +1282,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="17">
-        <v>21020</v>
-      </c>
-      <c r="D27" s="17">
+        <v>41</v>
+      </c>
+      <c r="C27" s="10">
+        <v>20642</v>
+      </c>
+      <c r="D27" s="10">
         <v>24000</v>
       </c>
-      <c r="E27" s="15"/>
-      <c r="F27" s="21"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="13"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
@@ -1290,16 +1300,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="17">
-        <v>21080</v>
-      </c>
-      <c r="D28" s="17">
+        <v>43</v>
+      </c>
+      <c r="C28" s="10">
+        <v>21020</v>
+      </c>
+      <c r="D28" s="10">
         <v>24000</v>
       </c>
-      <c r="E28" s="15"/>
-      <c r="F28" s="21"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="13"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
@@ -1308,16 +1318,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="17">
-        <v>17866</v>
-      </c>
-      <c r="D29" s="17">
-        <v>21000</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="21"/>
+        <v>39</v>
+      </c>
+      <c r="C29" s="10">
+        <v>21080</v>
+      </c>
+      <c r="D29" s="10">
+        <v>24000</v>
+      </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="13"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
@@ -1326,31 +1336,31 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="17">
-        <v>17822</v>
-      </c>
-      <c r="D30" s="17">
+        <v>10</v>
+      </c>
+      <c r="C30" s="10">
+        <v>17866</v>
+      </c>
+      <c r="D30" s="10">
         <v>21000</v>
       </c>
       <c r="E30" s="3"/>
+      <c r="F30" s="13"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="17">
-        <v>17982</v>
-      </c>
-      <c r="D31" s="17">
+        <v>11</v>
+      </c>
+      <c r="C31" s="10">
+        <v>17822</v>
+      </c>
+      <c r="D31" s="10">
         <v>21000</v>
       </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="21"/>
+      <c r="E31" s="3"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
@@ -1359,16 +1369,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="17">
-        <v>18033</v>
-      </c>
-      <c r="D32" s="17">
+        <v>34</v>
+      </c>
+      <c r="C32" s="10">
+        <v>17982</v>
+      </c>
+      <c r="D32" s="10">
         <v>21000</v>
       </c>
-      <c r="E32" s="15"/>
-      <c r="F32" s="21"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="13"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
@@ -1379,14 +1389,14 @@
       <c r="B33" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="10">
         <v>17763</v>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="10">
         <v>21000</v>
       </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="21"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="13"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
@@ -1397,14 +1407,14 @@
       <c r="B34" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="17">
+      <c r="C34" s="10">
         <v>18083</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="10">
         <v>21000</v>
       </c>
-      <c r="E34" s="15"/>
-      <c r="F34" s="21"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="13"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
@@ -1415,14 +1425,14 @@
       <c r="B35" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="17">
+      <c r="C35" s="10">
         <v>14758</v>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="10">
         <v>18000</v>
       </c>
       <c r="E35" s="3"/>
-      <c r="F35" s="21"/>
+      <c r="F35" s="13"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
@@ -1433,14 +1443,14 @@
       <c r="B36" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="17">
+      <c r="C36" s="10">
         <v>14692</v>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="10">
         <v>18000</v>
       </c>
       <c r="E36" s="3"/>
-      <c r="F36" s="21"/>
+      <c r="F36" s="13"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
@@ -1451,10 +1461,10 @@
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="17">
+      <c r="C37" s="10">
         <v>14948</v>
       </c>
-      <c r="D37" s="17">
+      <c r="D37" s="10">
         <v>18000</v>
       </c>
       <c r="E37" s="3"/>
@@ -1468,14 +1478,14 @@
       <c r="B38" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="17">
+      <c r="C38" s="10">
         <v>14556</v>
       </c>
-      <c r="D38" s="17">
+      <c r="D38" s="10">
         <v>18000</v>
       </c>
-      <c r="E38" s="15"/>
-      <c r="F38" s="21"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="13"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
@@ -1486,14 +1496,14 @@
       <c r="B39" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="17">
+      <c r="C39" s="10">
         <v>15013</v>
       </c>
-      <c r="D39" s="17">
+      <c r="D39" s="10">
         <v>18000</v>
       </c>
-      <c r="E39" s="15"/>
-      <c r="F39" s="21"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="13"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
@@ -1504,14 +1514,14 @@
       <c r="B40" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="17">
+      <c r="C40" s="10">
         <v>14527</v>
       </c>
-      <c r="D40" s="17">
+      <c r="D40" s="10">
         <v>18000</v>
       </c>
-      <c r="E40" s="15"/>
-      <c r="F40" s="21"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="13"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
@@ -1522,14 +1532,14 @@
       <c r="B41" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C41" s="17">
+      <c r="C41" s="10">
         <v>11999</v>
       </c>
-      <c r="D41" s="17">
+      <c r="D41" s="10">
         <v>15000</v>
       </c>
-      <c r="E41" s="15"/>
-      <c r="F41" s="21"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="13"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
@@ -1540,14 +1550,14 @@
       <c r="B42" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="17">
+      <c r="C42" s="10">
         <v>8659</v>
       </c>
-      <c r="D42" s="17">
+      <c r="D42" s="10">
         <v>12000</v>
       </c>
-      <c r="E42" s="15"/>
-      <c r="F42" s="21"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="13"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
@@ -1558,14 +1568,14 @@
       <c r="B43" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C43" s="17">
+      <c r="C43" s="10">
         <v>8433</v>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="10">
         <v>12000</v>
       </c>
-      <c r="E43" s="15"/>
-      <c r="F43" s="21"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="13"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
@@ -1574,12 +1584,12 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" s="17">
+        <v>52</v>
+      </c>
+      <c r="C44" s="10">
         <v>9122</v>
       </c>
-      <c r="D44" s="17">
+      <c r="D44" s="10">
         <v>12000</v>
       </c>
       <c r="G44" s="4"/>
@@ -1590,12 +1600,12 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C45" s="17">
+        <v>56</v>
+      </c>
+      <c r="C45" s="10">
         <v>8847</v>
       </c>
-      <c r="D45" s="17">
+      <c r="D45" s="10">
         <v>12000</v>
       </c>
       <c r="G45" s="4"/>
@@ -1606,12 +1616,12 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C46" s="17">
+        <v>57</v>
+      </c>
+      <c r="C46" s="10">
         <v>8677</v>
       </c>
-      <c r="D46" s="17">
+      <c r="D46" s="10">
         <v>12000</v>
       </c>
       <c r="G46" s="4"/>
@@ -1622,12 +1632,12 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C47" s="17">
+        <v>59</v>
+      </c>
+      <c r="C47" s="10">
         <v>9094</v>
       </c>
-      <c r="D47" s="17">
+      <c r="D47" s="10">
         <v>12000</v>
       </c>
       <c r="G47" s="4"/>
@@ -1638,12 +1648,12 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="17">
+        <v>54</v>
+      </c>
+      <c r="C48" s="10">
         <v>6112</v>
       </c>
-      <c r="D48" s="17">
+      <c r="D48" s="10">
         <v>9000</v>
       </c>
       <c r="G48" s="4"/>
@@ -1656,14 +1666,14 @@
       <c r="B49" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C49" s="17">
+      <c r="C49" s="10">
         <v>3024</v>
       </c>
-      <c r="D49" s="17">
+      <c r="D49" s="10">
         <v>6000</v>
       </c>
-      <c r="E49" s="15"/>
-      <c r="F49" s="21"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="13"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
@@ -1672,12 +1682,12 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C50" s="17">
+        <v>60</v>
+      </c>
+      <c r="C50" s="10">
         <v>2979</v>
       </c>
-      <c r="D50" s="17">
+      <c r="D50" s="10">
         <v>6000</v>
       </c>
       <c r="G50" s="4"/>
@@ -1688,12 +1698,12 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C51" s="17">
+        <v>53</v>
+      </c>
+      <c r="C51" s="10">
         <v>2954</v>
       </c>
-      <c r="D51" s="17">
+      <c r="D51" s="10">
         <v>6000</v>
       </c>
       <c r="G51" s="4"/>
@@ -1704,12 +1714,12 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C52" s="17">
+        <v>55</v>
+      </c>
+      <c r="C52" s="10">
         <v>975</v>
       </c>
-      <c r="D52" s="17">
+      <c r="D52" s="10">
         <v>3000</v>
       </c>
       <c r="G52" s="4"/>
@@ -1719,20 +1729,20 @@
       <c r="A53" s="2">
         <v>52</v>
       </c>
-      <c r="B53" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="C53" s="24">
+      <c r="B53" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" s="16">
         <v>982</v>
       </c>
-      <c r="D53" s="24">
+      <c r="D53" s="16">
         <v>3000</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F53" s="22" t="s">
-        <v>62</v>
+        <v>51</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>61</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBC5D0D-AD60-1445-A0C0-C85EF1528BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AC3B25-2440-204D-BF4A-48827AA7F814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1651,10 +1651,10 @@
         <v>54</v>
       </c>
       <c r="C48" s="10">
-        <v>6112</v>
+        <v>9071</v>
       </c>
       <c r="D48" s="10">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AC3B25-2440-204D-BF4A-48827AA7F814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C87231E-D424-E741-AD3F-5EAC0D6DA217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1011,16 +1011,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C11" s="12">
-        <v>36024</v>
+        <v>36088</v>
       </c>
       <c r="D11" s="12">
         <v>39000</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="13"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
@@ -1029,10 +1027,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C12" s="12">
-        <v>36148</v>
+        <v>36024</v>
       </c>
       <c r="D12" s="12">
         <v>39000</v>
@@ -1045,30 +1043,32 @@
         <v>12</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C13" s="12">
-        <v>36107</v>
+        <v>36148</v>
       </c>
       <c r="D13" s="12">
         <v>39000</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="3"/>
       <c r="F13" s="13"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="10">
-        <v>33042</v>
-      </c>
-      <c r="D14" s="10">
-        <v>36000</v>
-      </c>
+      <c r="B14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="12">
+        <v>36107</v>
+      </c>
+      <c r="D14" s="12">
+        <v>39000</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="13"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
@@ -1753,7 +1753,7 @@
     <row r="73" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F73">
-    <sortCondition descending="1" ref="D1:D73"/>
+    <sortCondition descending="1" ref="D1:D74"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C87231E-D424-E741-AD3F-5EAC0D6DA217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB6DC96-C688-2E40-A029-5FC558A605FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -903,10 +903,10 @@
         <v>23</v>
       </c>
       <c r="C5" s="11">
-        <v>44680</v>
+        <v>47730</v>
       </c>
       <c r="D5" s="11">
-        <v>48000</v>
+        <v>51000</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="13"/>
@@ -1250,14 +1250,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C25" s="10">
-        <v>20985</v>
+        <v>23982</v>
       </c>
       <c r="D25" s="10">
-        <v>24000</v>
-      </c>
+        <v>27000</v>
+      </c>
+      <c r="E25" s="8"/>
+      <c r="F25" s="13"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
@@ -1266,10 +1268,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C26" s="10">
-        <v>20909</v>
+        <v>20985</v>
       </c>
       <c r="D26" s="10">
         <v>24000</v>
@@ -1282,16 +1284,14 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C27" s="10">
-        <v>20642</v>
+        <v>20909</v>
       </c>
       <c r="D27" s="10">
         <v>24000</v>
       </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="13"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
@@ -1300,10 +1300,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C28" s="10">
-        <v>21020</v>
+        <v>20642</v>
       </c>
       <c r="D28" s="10">
         <v>24000</v>
@@ -1336,15 +1336,15 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C30" s="10">
-        <v>17866</v>
+        <v>20962</v>
       </c>
       <c r="D30" s="10">
-        <v>21000</v>
-      </c>
-      <c r="E30" s="3"/>
+        <v>24000</v>
+      </c>
+      <c r="E30" s="8"/>
       <c r="F30" s="13"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -1352,15 +1352,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C31" s="10">
-        <v>17822</v>
+        <v>17866</v>
       </c>
       <c r="D31" s="10">
         <v>21000</v>
       </c>
       <c r="E31" s="3"/>
+      <c r="F31" s="13"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
@@ -1369,16 +1370,15 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C32" s="10">
-        <v>17982</v>
+        <v>17822</v>
       </c>
       <c r="D32" s="10">
         <v>21000</v>
       </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="13"/>
+      <c r="E32" s="3"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
@@ -1753,7 +1753,7 @@
     <row r="73" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F73">
-    <sortCondition descending="1" ref="D1:D74"/>
+    <sortCondition descending="1" ref="D1:D73"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB6DC96-C688-2E40-A029-5FC558A605FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF08F68-87C9-D741-8307-82BABF0035F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1664,16 +1664,14 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C49" s="10">
-        <v>3024</v>
+        <v>5947</v>
       </c>
       <c r="D49" s="10">
-        <v>6000</v>
-      </c>
-      <c r="E49" s="8"/>
-      <c r="F49" s="13"/>
+        <v>9000</v>
+      </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
@@ -1682,14 +1680,16 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C50" s="10">
-        <v>2979</v>
+        <v>3024</v>
       </c>
       <c r="D50" s="10">
         <v>6000</v>
       </c>
+      <c r="E50" s="8"/>
+      <c r="F50" s="13"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
     </row>
@@ -1698,10 +1698,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C51" s="10">
-        <v>2954</v>
+        <v>2979</v>
       </c>
       <c r="D51" s="10">
         <v>6000</v>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF08F68-87C9-D741-8307-82BABF0035F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7E9492-9B9F-324F-9BBA-8208FC1CD37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -863,10 +863,10 @@
         <v>19</v>
       </c>
       <c r="C3" s="11">
-        <v>50950</v>
+        <v>53901</v>
       </c>
       <c r="D3" s="11">
-        <v>53000</v>
+        <v>57000</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" t="s">

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7E9492-9B9F-324F-9BBA-8208FC1CD37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191D203C-338A-2D4D-BCD4-55DEF5C4CE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1352,15 +1352,15 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C31" s="10">
-        <v>17866</v>
+        <v>20938</v>
       </c>
       <c r="D31" s="10">
-        <v>21000</v>
-      </c>
-      <c r="E31" s="3"/>
+        <v>24000</v>
+      </c>
+      <c r="E31" s="8"/>
       <c r="F31" s="13"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -1370,15 +1370,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32" s="10">
-        <v>17822</v>
+        <v>17866</v>
       </c>
       <c r="D32" s="10">
         <v>21000</v>
       </c>
       <c r="E32" s="3"/>
+      <c r="F32" s="13"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
@@ -1387,16 +1388,15 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C33" s="10">
-        <v>17763</v>
+        <v>17822</v>
       </c>
       <c r="D33" s="10">
         <v>21000</v>
       </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="13"/>
+      <c r="E33" s="3"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
@@ -1405,10 +1405,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C34" s="10">
-        <v>18083</v>
+        <v>17763</v>
       </c>
       <c r="D34" s="10">
         <v>21000</v>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191D203C-338A-2D4D-BCD4-55DEF5C4CE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D928CA-BD43-0F4E-9E9C-ADD5649E4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1321,10 +1321,10 @@
         <v>39</v>
       </c>
       <c r="C29" s="10">
-        <v>21080</v>
+        <v>24067</v>
       </c>
       <c r="D29" s="10">
-        <v>24000</v>
+        <v>27000</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="13"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D928CA-BD43-0F4E-9E9C-ADD5649E4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA8411A-49B2-6F48-A9C3-7D7B578FA286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -885,10 +885,10 @@
         <v>28</v>
       </c>
       <c r="C4" s="11">
-        <v>48003</v>
+        <v>50985</v>
       </c>
       <c r="D4" s="11">
-        <v>51000</v>
+        <v>54000</v>
       </c>
       <c r="G4" s="21"/>
       <c r="H4" s="22" t="s">
@@ -1268,14 +1268,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C26" s="10">
-        <v>20985</v>
+        <v>24067</v>
       </c>
       <c r="D26" s="10">
-        <v>24000</v>
-      </c>
+        <v>27000</v>
+      </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="13"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
@@ -1284,10 +1286,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C27" s="10">
-        <v>20909</v>
+        <v>20985</v>
       </c>
       <c r="D27" s="10">
         <v>24000</v>
@@ -1300,16 +1302,14 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C28" s="10">
-        <v>20642</v>
+        <v>20909</v>
       </c>
       <c r="D28" s="10">
         <v>24000</v>
       </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="13"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
@@ -1318,13 +1318,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C29" s="10">
-        <v>24067</v>
+        <v>20642</v>
       </c>
       <c r="D29" s="10">
-        <v>27000</v>
+        <v>24000</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="13"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA8411A-49B2-6F48-A9C3-7D7B578FA286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC67FB93-23D7-A74E-8276-DF2D0232E858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1289,10 +1289,10 @@
         <v>17</v>
       </c>
       <c r="C27" s="10">
-        <v>20985</v>
+        <v>23812</v>
       </c>
       <c r="D27" s="10">
-        <v>24000</v>
+        <v>27000</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC67FB93-23D7-A74E-8276-DF2D0232E858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57256F63-000E-E44D-B514-382C95570FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -941,10 +941,10 @@
         <v>24</v>
       </c>
       <c r="C7" s="11">
-        <v>41969</v>
+        <v>45036</v>
       </c>
       <c r="D7" s="11">
-        <v>45000</v>
+        <v>48000</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="13" t="s">
@@ -1548,16 +1548,14 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C42" s="10">
-        <v>8659</v>
+        <v>12030</v>
       </c>
       <c r="D42" s="10">
-        <v>12000</v>
-      </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="13"/>
+        <v>15000</v>
+      </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
@@ -1566,10 +1564,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C43" s="10">
-        <v>8433</v>
+        <v>8659</v>
       </c>
       <c r="D43" s="10">
         <v>12000</v>
@@ -1584,14 +1582,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C44" s="10">
-        <v>9122</v>
+        <v>8433</v>
       </c>
       <c r="D44" s="10">
         <v>12000</v>
       </c>
+      <c r="E44" s="8"/>
+      <c r="F44" s="13"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
     </row>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57256F63-000E-E44D-B514-382C95570FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1CA7CCA-D83A-4D44-B178-5FAC265242B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
   <si>
     <t>No.</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>Vehicle approaching high mileage</t>
+  </si>
+  <si>
+    <t>MR01JHGP</t>
   </si>
 </sst>
 </file>
@@ -799,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -1717,10 +1720,10 @@
         <v>55</v>
       </c>
       <c r="C52" s="10">
-        <v>975</v>
+        <v>2967</v>
       </c>
       <c r="D52" s="10">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -1729,31 +1732,47 @@
       <c r="A53" s="2">
         <v>52</v>
       </c>
-      <c r="B53" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53" s="16">
-        <v>982</v>
-      </c>
-      <c r="D53" s="16">
+      <c r="B53" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53" s="10">
+        <v>1060</v>
+      </c>
+      <c r="D53" s="10">
         <v>3000</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F53" s="14" t="s">
-        <v>61</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35"/>
-    <row r="71" x14ac:dyDescent="0.35"/>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" s="16">
+        <v>982</v>
+      </c>
+      <c r="D54" s="16">
+        <v>3000</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="65" x14ac:dyDescent="0.35"/>
     <row r="72" x14ac:dyDescent="0.35"/>
     <row r="73" x14ac:dyDescent="0.35"/>
+    <row r="74" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F73">
-    <sortCondition descending="1" ref="D1:D73"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
+    <sortCondition descending="1" ref="D1:D74"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1CA7CCA-D83A-4D44-B178-5FAC265242B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A041935-7675-D140-B3FE-CA74BADFB103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
   <si>
     <t>No.</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>MR01JHGP</t>
+  </si>
+  <si>
+    <t>Steering Stem was never replaced during accident repair &amp; Oil leak on the Right cover</t>
+  </si>
+  <si>
+    <t>Engine noise</t>
   </si>
 </sst>
 </file>
@@ -1110,16 +1116,17 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C17" s="10">
-        <v>29439</v>
+        <v>33048</v>
       </c>
       <c r="D17" s="10">
-        <v>33000</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="13"/>
+        <v>36000</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>66</v>
+      </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
@@ -1128,17 +1135,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C18" s="10">
-        <v>30014</v>
+        <v>29439</v>
       </c>
       <c r="D18" s="10">
         <v>33000</v>
       </c>
-      <c r="F18" s="13" t="s">
-        <v>63</v>
-      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="13"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
@@ -1506,7 +1512,9 @@
         <v>18000</v>
       </c>
       <c r="E39" s="8"/>
-      <c r="F39" s="13"/>
+      <c r="F39" s="13" t="s">
+        <v>67</v>
+      </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A041935-7675-D140-B3FE-CA74BADFB103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F05FDC7-A170-8D4D-B322-81D23E04F56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="67">
   <si>
     <t>No.</t>
   </si>
@@ -236,9 +236,6 @@
   </si>
   <si>
     <t>Steering Stem was never replaced during accident repair &amp; Oil leak on the Right cover</t>
-  </si>
-  <si>
-    <t>Engine noise</t>
   </si>
 </sst>
 </file>
@@ -970,10 +967,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="11">
-        <v>42086</v>
+        <v>44967</v>
       </c>
       <c r="D8" s="11">
-        <v>45000</v>
+        <v>48000</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="13"/>
@@ -1512,9 +1509,7 @@
         <v>18000</v>
       </c>
       <c r="E39" s="8"/>
-      <c r="F39" s="13" t="s">
-        <v>67</v>
-      </c>
+      <c r="F39" s="13"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F05FDC7-A170-8D4D-B322-81D23E04F56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8086977F-2583-BD49-BC77-EC90DFC45923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -847,10 +847,10 @@
         <v>14</v>
       </c>
       <c r="C2" s="11">
-        <v>54008</v>
+        <v>57062</v>
       </c>
       <c r="D2" s="11">
-        <v>57000</v>
+        <v>60000</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" t="s">

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8086977F-2583-BD49-BC77-EC90DFC45923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BB0935-FA25-1149-BBF7-E4F72603AEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -926,16 +926,18 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C6" s="11">
-        <v>45019</v>
+        <v>45036</v>
       </c>
       <c r="D6" s="11">
         <v>48000</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="13"/>
+      <c r="F6" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
@@ -944,18 +946,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C7" s="11">
-        <v>45036</v>
+        <v>45019</v>
       </c>
       <c r="D7" s="11">
         <v>48000</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="13" t="s">
-        <v>63</v>
-      </c>
+      <c r="F7" s="13"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
@@ -1017,14 +1017,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C11" s="12">
-        <v>36088</v>
+        <v>36148</v>
       </c>
       <c r="D11" s="12">
         <v>39000</v>
       </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="13"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
@@ -1033,15 +1035,15 @@
         <v>11</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C12" s="12">
-        <v>36024</v>
+        <v>36107</v>
       </c>
       <c r="D12" s="12">
         <v>39000</v>
       </c>
-      <c r="E12" s="3"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1049,31 +1051,29 @@
         <v>12</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C13" s="12">
-        <v>36148</v>
+        <v>36088</v>
       </c>
       <c r="D13" s="12">
         <v>39000</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C14" s="12">
-        <v>36107</v>
+        <v>36024</v>
       </c>
       <c r="D14" s="12">
         <v>39000</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="E14" s="3"/>
       <c r="F14" s="13"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -1097,33 +1097,33 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" s="10">
-        <v>33004</v>
+        <v>33048</v>
       </c>
       <c r="D16" s="10">
         <v>36000</v>
       </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="13"/>
+      <c r="F16" s="13" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C17" s="10">
-        <v>33048</v>
+        <v>33004</v>
       </c>
       <c r="D17" s="10">
         <v>36000</v>
       </c>
-      <c r="F17" s="13" t="s">
-        <v>66</v>
-      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="13"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
@@ -1168,14 +1168,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C20" s="10">
-        <v>23903</v>
+        <v>24261</v>
       </c>
       <c r="D20" s="10">
         <v>27000</v>
       </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="13"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
@@ -1184,10 +1186,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C21" s="10">
-        <v>23931</v>
+        <v>24067</v>
       </c>
       <c r="D21" s="10">
         <v>27000</v>
@@ -1220,10 +1222,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C23" s="10">
-        <v>23978</v>
+        <v>23982</v>
       </c>
       <c r="D23" s="10">
         <v>27000</v>
@@ -1238,10 +1240,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C24" s="10">
-        <v>24261</v>
+        <v>23978</v>
       </c>
       <c r="D24" s="10">
         <v>27000</v>
@@ -1256,10 +1258,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C25" s="10">
-        <v>23982</v>
+        <v>23931</v>
       </c>
       <c r="D25" s="10">
         <v>27000</v>
@@ -1274,16 +1276,14 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C26" s="10">
-        <v>24067</v>
+        <v>23903</v>
       </c>
       <c r="D26" s="10">
         <v>27000</v>
       </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="13"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
@@ -1308,14 +1308,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C28" s="10">
-        <v>20909</v>
+        <v>20962</v>
       </c>
       <c r="D28" s="10">
         <v>24000</v>
       </c>
+      <c r="E28" s="8"/>
+      <c r="F28" s="13"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
@@ -1324,10 +1326,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C29" s="10">
-        <v>20642</v>
+        <v>20938</v>
       </c>
       <c r="D29" s="10">
         <v>24000</v>
@@ -1342,26 +1344,24 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="C30" s="10">
-        <v>20962</v>
+        <v>20909</v>
       </c>
       <c r="D30" s="10">
         <v>24000</v>
       </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="13"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C31" s="10">
-        <v>20938</v>
+        <v>20642</v>
       </c>
       <c r="D31" s="10">
         <v>24000</v>
@@ -1429,15 +1429,15 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C35" s="10">
-        <v>14758</v>
+        <v>15013</v>
       </c>
       <c r="D35" s="10">
         <v>18000</v>
       </c>
-      <c r="E35" s="3"/>
+      <c r="E35" s="8"/>
       <c r="F35" s="13"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -1447,16 +1447,15 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C36" s="10">
-        <v>14692</v>
+        <v>14948</v>
       </c>
       <c r="D36" s="10">
         <v>18000</v>
       </c>
       <c r="E36" s="3"/>
-      <c r="F36" s="13"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
@@ -1465,15 +1464,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C37" s="10">
-        <v>14948</v>
+        <v>14758</v>
       </c>
       <c r="D37" s="10">
         <v>18000</v>
       </c>
       <c r="E37" s="3"/>
+      <c r="F37" s="13"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
@@ -1482,15 +1482,15 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C38" s="10">
-        <v>14556</v>
+        <v>14692</v>
       </c>
       <c r="D38" s="10">
         <v>18000</v>
       </c>
-      <c r="E38" s="8"/>
+      <c r="E38" s="3"/>
       <c r="F38" s="13"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -1500,10 +1500,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C39" s="10">
-        <v>15013</v>
+        <v>14556</v>
       </c>
       <c r="D39" s="10">
         <v>18000</v>
@@ -1536,16 +1536,14 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C41" s="10">
-        <v>11999</v>
+        <v>12030</v>
       </c>
       <c r="D41" s="10">
         <v>15000</v>
       </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="13"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
@@ -1554,14 +1552,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C42" s="10">
-        <v>12030</v>
+        <v>11999</v>
       </c>
       <c r="D42" s="10">
         <v>15000</v>
       </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="13"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
@@ -1570,16 +1570,14 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="C43" s="10">
-        <v>8659</v>
+        <v>11845</v>
       </c>
       <c r="D43" s="10">
-        <v>12000</v>
-      </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="13"/>
+        <v>15000</v>
+      </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
@@ -1588,16 +1586,14 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C44" s="10">
-        <v>8433</v>
+        <v>9094</v>
       </c>
       <c r="D44" s="10">
         <v>12000</v>
       </c>
-      <c r="E44" s="8"/>
-      <c r="F44" s="13"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
     </row>
@@ -1606,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C45" s="10">
-        <v>8847</v>
+        <v>9071</v>
       </c>
       <c r="D45" s="10">
         <v>12000</v>
@@ -1622,10 +1618,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C46" s="10">
-        <v>8677</v>
+        <v>8847</v>
       </c>
       <c r="D46" s="10">
         <v>12000</v>
@@ -1638,14 +1634,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C47" s="10">
-        <v>9094</v>
+        <v>8659</v>
       </c>
       <c r="D47" s="10">
         <v>12000</v>
       </c>
+      <c r="E47" s="8"/>
+      <c r="F47" s="13"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
     </row>
@@ -1654,14 +1652,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C48" s="10">
-        <v>9071</v>
+        <v>8433</v>
       </c>
       <c r="D48" s="10">
         <v>12000</v>
       </c>
+      <c r="E48" s="8"/>
+      <c r="F48" s="13"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
     </row>
@@ -1775,7 +1775,7 @@
     <row r="74" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
-    <sortCondition descending="1" ref="D1:D74"/>
+    <sortCondition descending="1" ref="C1:C74"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BB0935-FA25-1149-BBF7-E4F72603AEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60FACB5-2ED5-7342-9DB3-5E59CF82D918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -906,10 +906,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C5" s="11">
-        <v>47730</v>
+        <v>47913</v>
       </c>
       <c r="D5" s="11">
         <v>51000</v>
@@ -926,18 +926,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="11">
-        <v>45036</v>
+        <v>47730</v>
       </c>
       <c r="D6" s="11">
-        <v>48000</v>
+        <v>51000</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="13" t="s">
-        <v>63</v>
-      </c>
+      <c r="F6" s="13"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
@@ -946,16 +944,18 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C7" s="11">
-        <v>45019</v>
+        <v>45036</v>
       </c>
       <c r="D7" s="11">
         <v>48000</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="13"/>
+      <c r="F7" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
@@ -1168,13 +1168,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C20" s="10">
-        <v>24261</v>
+        <v>26965</v>
       </c>
       <c r="D20" s="10">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="13"/>
@@ -1186,10 +1186,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C21" s="10">
-        <v>24067</v>
+        <v>24261</v>
       </c>
       <c r="D21" s="10">
         <v>27000</v>
@@ -1204,10 +1204,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C22" s="10">
-        <v>23999</v>
+        <v>24067</v>
       </c>
       <c r="D22" s="10">
         <v>27000</v>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60FACB5-2ED5-7342-9DB3-5E59CF82D918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D8C658-38B0-DE45-8D5C-3EE345D35383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -977,18 +977,18 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="12">
-        <v>38988</v>
-      </c>
-      <c r="D9" s="12">
-        <v>42000</v>
+      <c r="C9" s="11">
+        <v>41984</v>
+      </c>
+      <c r="D9" s="11">
+        <v>45000</v>
       </c>
       <c r="E9" s="6"/>
       <c r="G9" s="4"/>
@@ -1114,10 +1114,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C17" s="10">
-        <v>33004</v>
+        <v>33033</v>
       </c>
       <c r="D17" s="10">
         <v>36000</v>
@@ -1132,13 +1132,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C18" s="10">
-        <v>29439</v>
+        <v>33004</v>
       </c>
       <c r="D18" s="10">
-        <v>33000</v>
+        <v>36000</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="13"/>
@@ -1308,10 +1308,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" s="10">
-        <v>20962</v>
+        <v>20987</v>
       </c>
       <c r="D28" s="10">
         <v>24000</v>
@@ -1326,10 +1326,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C29" s="10">
-        <v>20938</v>
+        <v>20962</v>
       </c>
       <c r="D29" s="10">
         <v>24000</v>
@@ -1344,30 +1344,30 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="C30" s="10">
-        <v>20909</v>
+        <v>20938</v>
       </c>
       <c r="D30" s="10">
         <v>24000</v>
       </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="13"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C31" s="10">
-        <v>20642</v>
+        <v>20909</v>
       </c>
       <c r="D31" s="10">
         <v>24000</v>
       </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="13"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
@@ -1376,15 +1376,15 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C32" s="10">
-        <v>17866</v>
+        <v>20642</v>
       </c>
       <c r="D32" s="10">
-        <v>21000</v>
-      </c>
-      <c r="E32" s="3"/>
+        <v>24000</v>
+      </c>
+      <c r="E32" s="8"/>
       <c r="F32" s="13"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -1394,15 +1394,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="10">
-        <v>17822</v>
+        <v>17866</v>
       </c>
       <c r="D33" s="10">
         <v>21000</v>
       </c>
       <c r="E33" s="3"/>
+      <c r="F33" s="13"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
@@ -1411,16 +1412,15 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C34" s="10">
-        <v>17763</v>
+        <v>17822</v>
       </c>
       <c r="D34" s="10">
         <v>21000</v>
       </c>
-      <c r="E34" s="8"/>
-      <c r="F34" s="13"/>
+      <c r="E34" s="3"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D8C658-38B0-DE45-8D5C-3EE345D35383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56848F12-E9CA-C24C-9296-ADE1D1C74C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1222,10 +1222,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="10">
-        <v>23982</v>
+        <v>24062</v>
       </c>
       <c r="D23" s="10">
         <v>27000</v>
@@ -1240,10 +1240,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C24" s="10">
-        <v>23978</v>
+        <v>23982</v>
       </c>
       <c r="D24" s="10">
         <v>27000</v>
@@ -1258,10 +1258,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C25" s="10">
-        <v>23931</v>
+        <v>23978</v>
       </c>
       <c r="D25" s="10">
         <v>27000</v>
@@ -1276,14 +1276,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C26" s="10">
-        <v>23903</v>
+        <v>23931</v>
       </c>
       <c r="D26" s="10">
         <v>27000</v>
       </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="13"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
@@ -1292,10 +1294,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C27" s="10">
-        <v>23812</v>
+        <v>23903</v>
       </c>
       <c r="D27" s="10">
         <v>27000</v>
@@ -1308,16 +1310,14 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C28" s="10">
-        <v>20987</v>
+        <v>23812</v>
       </c>
       <c r="D28" s="10">
-        <v>24000</v>
-      </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="13"/>
+        <v>27000</v>
+      </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
@@ -1326,10 +1326,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C29" s="10">
-        <v>20962</v>
+        <v>20987</v>
       </c>
       <c r="D29" s="10">
         <v>24000</v>
@@ -1344,10 +1344,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C30" s="10">
-        <v>20938</v>
+        <v>20962</v>
       </c>
       <c r="D30" s="10">
         <v>24000</v>
@@ -1360,14 +1360,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="C31" s="10">
-        <v>20909</v>
+        <v>20938</v>
       </c>
       <c r="D31" s="10">
         <v>24000</v>
       </c>
+      <c r="E31" s="8"/>
+      <c r="F31" s="13"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
@@ -1376,16 +1378,14 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C32" s="10">
-        <v>20642</v>
+        <v>20909</v>
       </c>
       <c r="D32" s="10">
         <v>24000</v>
       </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="13"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56848F12-E9CA-C24C-9296-ADE1D1C74C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C4EBF5-A054-824A-B720-A45DD59B3BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1310,14 +1310,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C28" s="10">
-        <v>23812</v>
+        <v>23837</v>
       </c>
       <c r="D28" s="10">
         <v>27000</v>
       </c>
+      <c r="E28" s="8"/>
+      <c r="F28" s="13"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
@@ -1326,16 +1328,14 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C29" s="10">
-        <v>20987</v>
+        <v>23812</v>
       </c>
       <c r="D29" s="10">
-        <v>24000</v>
-      </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="13"/>
+        <v>27000</v>
+      </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
@@ -1344,10 +1344,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="10">
-        <v>20962</v>
+        <v>20987</v>
       </c>
       <c r="D30" s="10">
         <v>24000</v>
@@ -1360,10 +1360,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C31" s="10">
-        <v>20938</v>
+        <v>20962</v>
       </c>
       <c r="D31" s="10">
         <v>24000</v>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C4EBF5-A054-824A-B720-A45DD59B3BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45F6F0F-A441-C24B-BA35-AE1E012B2728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1344,10 +1344,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C30" s="10">
-        <v>20987</v>
+        <v>21210</v>
       </c>
       <c r="D30" s="10">
         <v>24000</v>
@@ -1360,10 +1360,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31" s="10">
-        <v>20962</v>
+        <v>20987</v>
       </c>
       <c r="D31" s="10">
         <v>24000</v>
@@ -1378,14 +1378,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C32" s="10">
-        <v>20909</v>
+        <v>20962</v>
       </c>
       <c r="D32" s="10">
         <v>24000</v>
       </c>
+      <c r="E32" s="8"/>
+      <c r="F32" s="13"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
@@ -1394,16 +1396,14 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C33" s="10">
-        <v>17866</v>
+        <v>20909</v>
       </c>
       <c r="D33" s="10">
-        <v>21000</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="13"/>
+        <v>24000</v>
+      </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
@@ -1412,15 +1412,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="10">
-        <v>17822</v>
+        <v>20842</v>
       </c>
       <c r="D34" s="10">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="E34" s="3"/>
+      <c r="F34" s="13"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
@@ -1429,16 +1430,15 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="C35" s="10">
-        <v>15013</v>
+        <v>17822</v>
       </c>
       <c r="D35" s="10">
-        <v>18000</v>
-      </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="13"/>
+        <v>21000</v>
+      </c>
+      <c r="E35" s="3"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
@@ -1447,15 +1447,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="C36" s="10">
-        <v>14948</v>
+        <v>15013</v>
       </c>
       <c r="D36" s="10">
         <v>18000</v>
       </c>
-      <c r="E36" s="3"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="13"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
@@ -1464,16 +1465,15 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C37" s="10">
-        <v>14758</v>
+        <v>14948</v>
       </c>
       <c r="D37" s="10">
         <v>18000</v>
       </c>
       <c r="E37" s="3"/>
-      <c r="F37" s="13"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
@@ -1482,10 +1482,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C38" s="10">
-        <v>14692</v>
+        <v>14758</v>
       </c>
       <c r="D38" s="10">
         <v>18000</v>
@@ -1500,15 +1500,15 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C39" s="10">
-        <v>14556</v>
+        <v>14692</v>
       </c>
       <c r="D39" s="10">
         <v>18000</v>
       </c>
-      <c r="E39" s="8"/>
+      <c r="E39" s="3"/>
       <c r="F39" s="13"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -1518,10 +1518,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C40" s="10">
-        <v>14527</v>
+        <v>14556</v>
       </c>
       <c r="D40" s="10">
         <v>18000</v>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45F6F0F-A441-C24B-BA35-AE1E012B2728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6A862A-CAF5-984D-8AF5-0200C9F7459F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1482,16 +1482,14 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="C38" s="10">
-        <v>14758</v>
+        <v>14922</v>
       </c>
       <c r="D38" s="10">
         <v>18000</v>
       </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="13"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
@@ -1500,10 +1498,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C39" s="10">
-        <v>14692</v>
+        <v>14758</v>
       </c>
       <c r="D39" s="10">
         <v>18000</v>
@@ -1518,15 +1516,15 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C40" s="10">
-        <v>14556</v>
+        <v>14692</v>
       </c>
       <c r="D40" s="10">
         <v>18000</v>
       </c>
-      <c r="E40" s="8"/>
+      <c r="E40" s="3"/>
       <c r="F40" s="13"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -1536,14 +1534,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C41" s="10">
-        <v>12030</v>
+        <v>14556</v>
       </c>
       <c r="D41" s="10">
-        <v>15000</v>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="E41" s="8"/>
+      <c r="F41" s="13"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
@@ -1552,16 +1552,14 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C42" s="10">
-        <v>11999</v>
+        <v>12030</v>
       </c>
       <c r="D42" s="10">
         <v>15000</v>
       </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="13"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
@@ -1570,14 +1568,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C43" s="10">
-        <v>11845</v>
+        <v>11999</v>
       </c>
       <c r="D43" s="10">
         <v>15000</v>
       </c>
+      <c r="E43" s="8"/>
+      <c r="F43" s="13"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
@@ -1586,13 +1586,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C44" s="10">
-        <v>9094</v>
+        <v>11845</v>
       </c>
       <c r="D44" s="10">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6A862A-CAF5-984D-8AF5-0200C9F7459F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B201B0D-EA37-6C4B-B48B-18A602381DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -999,10 +999,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="12">
-        <v>38901</v>
+        <v>39038</v>
       </c>
       <c r="D10" s="12">
         <v>42000</v>
@@ -1017,13 +1017,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C11" s="12">
-        <v>36148</v>
+        <v>38901</v>
       </c>
       <c r="D11" s="12">
-        <v>39000</v>
+        <v>42000</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="13"/>
@@ -1035,15 +1035,15 @@
         <v>11</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C12" s="12">
-        <v>36107</v>
+        <v>36148</v>
       </c>
       <c r="D12" s="12">
         <v>39000</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="3"/>
       <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1051,43 +1051,43 @@
         <v>12</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C13" s="12">
-        <v>36088</v>
+        <v>36107</v>
       </c>
       <c r="D13" s="12">
         <v>39000</v>
       </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C14" s="12">
-        <v>36024</v>
+        <v>36088</v>
       </c>
       <c r="D14" s="12">
         <v>39000</v>
       </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="13"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="10">
-        <v>33062</v>
-      </c>
-      <c r="D15" s="10">
-        <v>36000</v>
+      <c r="C15" s="12">
+        <v>35899</v>
+      </c>
+      <c r="D15" s="12">
+        <v>39000</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="13"/>
@@ -1153,10 +1153,10 @@
         <v>48</v>
       </c>
       <c r="C19" s="10">
-        <v>27165</v>
+        <v>29989</v>
       </c>
       <c r="D19" s="10">
-        <v>30000</v>
+        <v>33000</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="13"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B201B0D-EA37-6C4B-B48B-18A602381DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EEABA5-1C6D-D94B-BBF6-DB3C328D05F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1017,15 +1017,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12">
-        <v>38901</v>
+        <v>38912</v>
       </c>
       <c r="D11" s="12">
         <v>42000</v>
       </c>
-      <c r="E11" s="3"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="13"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -1035,13 +1035,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C12" s="12">
-        <v>36148</v>
+        <v>38901</v>
       </c>
       <c r="D12" s="12">
-        <v>39000</v>
+        <v>42000</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="13"/>
@@ -1051,15 +1051,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C13" s="12">
-        <v>36107</v>
+        <v>36148</v>
       </c>
       <c r="D13" s="12">
         <v>39000</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="3"/>
       <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EEABA5-1C6D-D94B-BBF6-DB3C328D05F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EEAB96E-D740-A84F-95BC-2F9F7B73EB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1135,10 +1135,10 @@
         <v>15</v>
       </c>
       <c r="C18" s="10">
-        <v>33004</v>
+        <v>36093</v>
       </c>
       <c r="D18" s="10">
-        <v>36000</v>
+        <v>39000</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="13"/>
@@ -1243,10 +1243,10 @@
         <v>43</v>
       </c>
       <c r="C24" s="10">
-        <v>23982</v>
+        <v>27004</v>
       </c>
       <c r="D24" s="10">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="13"/>
@@ -1689,10 +1689,10 @@
         <v>36</v>
       </c>
       <c r="C50" s="10">
-        <v>3024</v>
+        <v>8977</v>
       </c>
       <c r="D50" s="10">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="E50" s="8"/>
       <c r="F50" s="13"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EEAB96E-D740-A84F-95BC-2F9F7B73EB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22454628-22F0-8F4A-AD47-668C3FFDEBD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Fleet Mileage" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22454628-22F0-8F4A-AD47-668C3FFDEBD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8675B97F-D4B2-BF4D-8BC5-170F18ACE6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Fleet Mileage" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -806,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -1466,15 +1465,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C37" s="10">
-        <v>14948</v>
+        <v>14955</v>
       </c>
       <c r="D37" s="10">
         <v>18000</v>
       </c>
-      <c r="E37" s="3"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="13"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
@@ -1483,14 +1483,15 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="C38" s="10">
-        <v>14922</v>
+        <v>14948</v>
       </c>
       <c r="D38" s="10">
         <v>18000</v>
       </c>
+      <c r="E38" s="3"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
@@ -1499,16 +1500,14 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="C39" s="10">
-        <v>14758</v>
+        <v>14922</v>
       </c>
       <c r="D39" s="10">
         <v>18000</v>
       </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="13"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
@@ -1517,10 +1516,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C40" s="10">
-        <v>14692</v>
+        <v>14758</v>
       </c>
       <c r="D40" s="10">
         <v>18000</v>
@@ -1535,15 +1534,15 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C41" s="10">
-        <v>14556</v>
+        <v>14692</v>
       </c>
       <c r="D41" s="10">
         <v>18000</v>
       </c>
-      <c r="E41" s="8"/>
+      <c r="E41" s="3"/>
       <c r="F41" s="13"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -1553,14 +1552,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C42" s="10">
-        <v>12030</v>
+        <v>14556</v>
       </c>
       <c r="D42" s="10">
-        <v>15000</v>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="13"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
@@ -1569,16 +1570,14 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C43" s="10">
-        <v>11999</v>
+        <v>12030</v>
       </c>
       <c r="D43" s="10">
         <v>15000</v>
       </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="13"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
@@ -1770,10 +1769,12 @@
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
     </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="65" x14ac:dyDescent="0.35"/>
     <row r="72" x14ac:dyDescent="0.35"/>
     <row r="73" x14ac:dyDescent="0.35"/>
     <row r="74" x14ac:dyDescent="0.35"/>
+    <row r="75" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
     <sortCondition descending="1" ref="C1:C74"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8675B97F-D4B2-BF4D-8BC5-170F18ACE6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B493204-0228-1540-BBC2-08EEBDC3EC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -805,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -1168,10 +1168,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C20" s="10">
-        <v>26965</v>
+        <v>27101</v>
       </c>
       <c r="D20" s="10">
         <v>30000</v>
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C21" s="10">
-        <v>24261</v>
+        <v>26965</v>
       </c>
       <c r="D21" s="10">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="13"/>
@@ -1586,10 +1586,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C44" s="10">
-        <v>11845</v>
+        <v>12015</v>
       </c>
       <c r="D44" s="10">
         <v>15000</v>
@@ -1602,13 +1602,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C45" s="10">
-        <v>9071</v>
+        <v>11845</v>
       </c>
       <c r="D45" s="10">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -1771,10 +1771,6 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="65" x14ac:dyDescent="0.35"/>
-    <row r="72" x14ac:dyDescent="0.35"/>
-    <row r="73" x14ac:dyDescent="0.35"/>
-    <row r="74" x14ac:dyDescent="0.35"/>
-    <row r="75" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
     <sortCondition descending="1" ref="C1:C74"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B493204-0228-1540-BBC2-08EEBDC3EC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A3676A-1244-2A4D-B38D-D2963931C5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -805,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -1168,13 +1168,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C20" s="10">
-        <v>27101</v>
+        <v>28960</v>
       </c>
       <c r="D20" s="10">
-        <v>30000</v>
+        <v>33000</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="13"/>
@@ -1186,10 +1186,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C21" s="10">
-        <v>26965</v>
+        <v>27101</v>
       </c>
       <c r="D21" s="10">
         <v>30000</v>
@@ -1344,44 +1344,42 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C30" s="10">
-        <v>21210</v>
+        <v>23750</v>
       </c>
       <c r="D30" s="10">
-        <v>24000</v>
-      </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="13"/>
+        <v>27000</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C31" s="10">
-        <v>20987</v>
+        <v>21210</v>
       </c>
       <c r="D31" s="10">
         <v>24000</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="13"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="10">
-        <v>20962</v>
+        <v>20987</v>
       </c>
       <c r="D32" s="10">
         <v>24000</v>
@@ -1465,10 +1463,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C37" s="10">
-        <v>14955</v>
+        <v>15001</v>
       </c>
       <c r="D37" s="10">
         <v>18000</v>
@@ -1483,15 +1481,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C38" s="10">
-        <v>14948</v>
+        <v>14955</v>
       </c>
       <c r="D38" s="10">
         <v>18000</v>
       </c>
-      <c r="E38" s="3"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="13"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
@@ -1500,14 +1499,15 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="C39" s="10">
-        <v>14922</v>
+        <v>14948</v>
       </c>
       <c r="D39" s="10">
         <v>18000</v>
       </c>
+      <c r="E39" s="3"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
@@ -1516,16 +1516,14 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="C40" s="10">
-        <v>14758</v>
+        <v>14922</v>
       </c>
       <c r="D40" s="10">
         <v>18000</v>
       </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="13"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
@@ -1534,10 +1532,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C41" s="10">
-        <v>14692</v>
+        <v>14758</v>
       </c>
       <c r="D41" s="10">
         <v>18000</v>
@@ -1552,15 +1550,15 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C42" s="10">
-        <v>14556</v>
+        <v>14692</v>
       </c>
       <c r="D42" s="10">
         <v>18000</v>
       </c>
-      <c r="E42" s="8"/>
+      <c r="E42" s="3"/>
       <c r="F42" s="13"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -1570,14 +1568,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C43" s="10">
-        <v>12030</v>
+        <v>14556</v>
       </c>
       <c r="D43" s="10">
-        <v>15000</v>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="E43" s="8"/>
+      <c r="F43" s="13"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
@@ -1771,6 +1771,9 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="65" x14ac:dyDescent="0.35"/>
+    <row r="66" x14ac:dyDescent="0.35"/>
+    <row r="67" x14ac:dyDescent="0.35"/>
+    <row r="68" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
     <sortCondition descending="1" ref="C1:C74"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A3676A-1244-2A4D-B38D-D2963931C5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B6064A-6782-BC42-8A91-A7C3546EE0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -805,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -1481,10 +1481,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C38" s="10">
-        <v>14955</v>
+        <v>14977</v>
       </c>
       <c r="D38" s="10">
         <v>18000</v>
@@ -1499,15 +1499,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C39" s="10">
-        <v>14948</v>
+        <v>14955</v>
       </c>
       <c r="D39" s="10">
         <v>18000</v>
       </c>
-      <c r="E39" s="3"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="13"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
@@ -1516,14 +1517,15 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="C40" s="10">
-        <v>14922</v>
+        <v>14948</v>
       </c>
       <c r="D40" s="10">
         <v>18000</v>
       </c>
+      <c r="E40" s="3"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
@@ -1532,16 +1534,14 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="C41" s="10">
-        <v>14758</v>
+        <v>14922</v>
       </c>
       <c r="D41" s="10">
         <v>18000</v>
       </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="13"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
@@ -1550,10 +1550,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C42" s="10">
-        <v>14692</v>
+        <v>14758</v>
       </c>
       <c r="D42" s="10">
         <v>18000</v>
@@ -1568,15 +1568,15 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C43" s="10">
-        <v>14556</v>
+        <v>14692</v>
       </c>
       <c r="D43" s="10">
         <v>18000</v>
       </c>
-      <c r="E43" s="8"/>
+      <c r="E43" s="3"/>
       <c r="F43" s="13"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -1586,14 +1586,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C44" s="10">
-        <v>12015</v>
+        <v>14556</v>
       </c>
       <c r="D44" s="10">
-        <v>15000</v>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="E44" s="8"/>
+      <c r="F44" s="13"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
     </row>
@@ -1602,10 +1604,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C45" s="10">
-        <v>11845</v>
+        <v>12015</v>
       </c>
       <c r="D45" s="10">
         <v>15000</v>
@@ -1618,13 +1620,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C46" s="10">
-        <v>8847</v>
+        <v>11845</v>
       </c>
       <c r="D46" s="10">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -1774,6 +1776,7 @@
     <row r="66" x14ac:dyDescent="0.35"/>
     <row r="67" x14ac:dyDescent="0.35"/>
     <row r="68" x14ac:dyDescent="0.35"/>
+    <row r="69" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
     <sortCondition descending="1" ref="C1:C74"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B6064A-6782-BC42-8A91-A7C3546EE0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B485C8A-4BBB-1F4E-988E-464627590F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -805,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -1168,10 +1168,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C20" s="10">
-        <v>28960</v>
+        <v>29923</v>
       </c>
       <c r="D20" s="10">
         <v>33000</v>
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C21" s="10">
-        <v>27101</v>
+        <v>28960</v>
       </c>
       <c r="D21" s="10">
-        <v>30000</v>
+        <v>33000</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="13"/>
@@ -1204,13 +1204,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C22" s="10">
-        <v>24067</v>
+        <v>27101</v>
       </c>
       <c r="D22" s="10">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="13"/>
@@ -1222,10 +1222,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C23" s="10">
-        <v>24062</v>
+        <v>24067</v>
       </c>
       <c r="D23" s="10">
         <v>27000</v>
@@ -1240,13 +1240,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C24" s="10">
-        <v>27004</v>
+        <v>24062</v>
       </c>
       <c r="D24" s="10">
-        <v>30000</v>
+        <v>27000</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="13"/>
@@ -1258,13 +1258,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C25" s="10">
-        <v>23978</v>
+        <v>27004</v>
       </c>
       <c r="D25" s="10">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="13"/>
@@ -1276,10 +1276,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C26" s="10">
-        <v>23931</v>
+        <v>23978</v>
       </c>
       <c r="D26" s="10">
         <v>27000</v>
@@ -1777,6 +1777,7 @@
     <row r="67" x14ac:dyDescent="0.35"/>
     <row r="68" x14ac:dyDescent="0.35"/>
     <row r="69" x14ac:dyDescent="0.35"/>
+    <row r="70" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
     <sortCondition descending="1" ref="C1:C74"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B485C8A-4BBB-1F4E-988E-464627590F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534B20AB-7699-E448-9DE6-F9AC35F83118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -805,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -1636,16 +1636,14 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C47" s="10">
-        <v>8659</v>
+        <v>8847</v>
       </c>
       <c r="D47" s="10">
         <v>12000</v>
       </c>
-      <c r="E47" s="8"/>
-      <c r="F47" s="13"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
     </row>
@@ -1654,10 +1652,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C48" s="10">
-        <v>8433</v>
+        <v>8659</v>
       </c>
       <c r="D48" s="10">
         <v>12000</v>
@@ -1672,14 +1670,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C49" s="10">
-        <v>5947</v>
+        <v>8433</v>
       </c>
       <c r="D49" s="10">
-        <v>9000</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="E49" s="8"/>
+      <c r="F49" s="13"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
@@ -1778,6 +1778,7 @@
     <row r="68" x14ac:dyDescent="0.35"/>
     <row r="69" x14ac:dyDescent="0.35"/>
     <row r="70" x14ac:dyDescent="0.35"/>
+    <row r="71" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
     <sortCondition descending="1" ref="C1:C74"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534B20AB-7699-E448-9DE6-F9AC35F83118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911AE9A0-8C95-EC44-999E-44C201C579EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -805,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -1294,14 +1294,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C27" s="10">
-        <v>23903</v>
+        <v>23955</v>
       </c>
       <c r="D27" s="10">
         <v>27000</v>
       </c>
+      <c r="E27" s="8"/>
+      <c r="F27" s="13"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
@@ -1310,16 +1312,14 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C28" s="10">
-        <v>23837</v>
+        <v>23903</v>
       </c>
       <c r="D28" s="10">
         <v>27000</v>
       </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="13"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
@@ -1328,14 +1328,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C29" s="10">
-        <v>23812</v>
+        <v>23837</v>
       </c>
       <c r="D29" s="10">
         <v>27000</v>
       </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="13"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
@@ -1344,10 +1346,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C30" s="10">
-        <v>23750</v>
+        <v>23812</v>
       </c>
       <c r="D30" s="10">
         <v>27000</v>
@@ -1360,48 +1362,48 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C31" s="10">
-        <v>21210</v>
+        <v>23750</v>
       </c>
       <c r="D31" s="10">
-        <v>24000</v>
-      </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="13"/>
+        <v>27000</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C32" s="10">
-        <v>20987</v>
+        <v>21210</v>
       </c>
       <c r="D32" s="10">
         <v>24000</v>
       </c>
       <c r="E32" s="8"/>
       <c r="F32" s="13"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="C33" s="10">
-        <v>20909</v>
+        <v>20987</v>
       </c>
       <c r="D33" s="10">
         <v>24000</v>
       </c>
+      <c r="E33" s="8"/>
+      <c r="F33" s="13"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
@@ -1428,15 +1430,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C35" s="10">
-        <v>17822</v>
+        <v>18055</v>
       </c>
       <c r="D35" s="10">
         <v>21000</v>
       </c>
       <c r="E35" s="3"/>
+      <c r="F35" s="13"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
@@ -1445,16 +1448,15 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="C36" s="10">
-        <v>15013</v>
+        <v>17822</v>
       </c>
       <c r="D36" s="10">
-        <v>18000</v>
-      </c>
-      <c r="E36" s="8"/>
-      <c r="F36" s="13"/>
+        <v>21000</v>
+      </c>
+      <c r="E36" s="3"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
@@ -1463,10 +1465,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C37" s="10">
-        <v>15001</v>
+        <v>15013</v>
       </c>
       <c r="D37" s="10">
         <v>18000</v>
@@ -1481,10 +1483,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C38" s="10">
-        <v>14977</v>
+        <v>15001</v>
       </c>
       <c r="D38" s="10">
         <v>18000</v>
@@ -1499,10 +1501,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C39" s="10">
-        <v>14955</v>
+        <v>14977</v>
       </c>
       <c r="D39" s="10">
         <v>18000</v>
@@ -1517,15 +1519,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C40" s="10">
-        <v>14948</v>
+        <v>14955</v>
       </c>
       <c r="D40" s="10">
         <v>18000</v>
       </c>
-      <c r="E40" s="3"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="13"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
@@ -1779,6 +1782,8 @@
     <row r="69" x14ac:dyDescent="0.35"/>
     <row r="70" x14ac:dyDescent="0.35"/>
     <row r="71" x14ac:dyDescent="0.35"/>
+    <row r="72" x14ac:dyDescent="0.35"/>
+    <row r="73" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
     <sortCondition descending="1" ref="C1:C74"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911AE9A0-8C95-EC44-999E-44C201C579EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D823E159-9EFD-DC46-ADFD-A0D2A584EF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -805,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -1279,10 +1279,10 @@
         <v>49</v>
       </c>
       <c r="C26" s="10">
-        <v>23978</v>
+        <v>26924</v>
       </c>
       <c r="D26" s="10">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="13"/>
@@ -1448,15 +1448,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="C36" s="10">
-        <v>17822</v>
+        <v>17994</v>
       </c>
       <c r="D36" s="10">
         <v>21000</v>
       </c>
       <c r="E36" s="3"/>
+      <c r="F36" s="13"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
@@ -1465,16 +1466,15 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="C37" s="10">
-        <v>15013</v>
+        <v>17822</v>
       </c>
       <c r="D37" s="10">
-        <v>18000</v>
-      </c>
-      <c r="E37" s="8"/>
-      <c r="F37" s="13"/>
+        <v>21000</v>
+      </c>
+      <c r="E37" s="3"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
@@ -1784,6 +1784,7 @@
     <row r="71" x14ac:dyDescent="0.35"/>
     <row r="72" x14ac:dyDescent="0.35"/>
     <row r="73" x14ac:dyDescent="0.35"/>
+    <row r="74" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
     <sortCondition descending="1" ref="C1:C74"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D823E159-9EFD-DC46-ADFD-A0D2A584EF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D4B12E-126E-2447-9262-A89D1B78A459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -805,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -999,16 +999,15 @@
         <v>9</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C10" s="12">
-        <v>39038</v>
+        <v>39096</v>
       </c>
       <c r="D10" s="12">
         <v>42000</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="13"/>
+      <c r="E10" s="6"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
@@ -1017,15 +1016,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" s="12">
-        <v>38912</v>
+        <v>39038</v>
       </c>
       <c r="D11" s="12">
         <v>42000</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="3"/>
       <c r="F11" s="13"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -1035,29 +1034,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" s="12">
-        <v>38901</v>
+        <v>38912</v>
       </c>
       <c r="D12" s="12">
         <v>42000</v>
       </c>
-      <c r="E12" s="3"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="13"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C13" s="12">
-        <v>36148</v>
+        <v>38901</v>
       </c>
       <c r="D13" s="12">
-        <v>39000</v>
+        <v>42000</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="13"/>
@@ -1067,14 +1068,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C14" s="12">
-        <v>36088</v>
+        <v>36148</v>
       </c>
       <c r="D14" s="12">
         <v>39000</v>
       </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="13"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
@@ -1712,10 +1715,10 @@
         <v>60</v>
       </c>
       <c r="C51" s="10">
-        <v>2979</v>
+        <v>6044</v>
       </c>
       <c r="D51" s="10">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -1785,6 +1788,7 @@
     <row r="72" x14ac:dyDescent="0.35"/>
     <row r="73" x14ac:dyDescent="0.35"/>
     <row r="74" x14ac:dyDescent="0.35"/>
+    <row r="75" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
     <sortCondition descending="1" ref="C1:C74"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D4B12E-126E-2447-9262-A89D1B78A459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D63D98-F650-9540-A2FE-C7BC8D677554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -805,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -1486,16 +1486,15 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C38" s="10">
-        <v>15001</v>
+        <v>17786</v>
       </c>
       <c r="D38" s="10">
-        <v>18000</v>
-      </c>
-      <c r="E38" s="8"/>
-      <c r="F38" s="13"/>
+        <v>21000</v>
+      </c>
+      <c r="E38" s="3"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
@@ -1504,10 +1503,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C39" s="10">
-        <v>14977</v>
+        <v>15001</v>
       </c>
       <c r="D39" s="10">
         <v>18000</v>
@@ -1522,10 +1521,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C40" s="10">
-        <v>14955</v>
+        <v>14977</v>
       </c>
       <c r="D40" s="10">
         <v>18000</v>
@@ -1540,14 +1539,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C41" s="10">
-        <v>14922</v>
+        <v>14955</v>
       </c>
       <c r="D41" s="10">
         <v>18000</v>
       </c>
+      <c r="E41" s="8"/>
+      <c r="F41" s="13"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
@@ -1556,16 +1557,14 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="C42" s="10">
-        <v>14758</v>
+        <v>14922</v>
       </c>
       <c r="D42" s="10">
         <v>18000</v>
       </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="13"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
@@ -1574,10 +1573,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C43" s="10">
-        <v>14692</v>
+        <v>14758</v>
       </c>
       <c r="D43" s="10">
         <v>18000</v>
@@ -1592,15 +1591,15 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C44" s="10">
-        <v>14556</v>
+        <v>14692</v>
       </c>
       <c r="D44" s="10">
         <v>18000</v>
       </c>
-      <c r="E44" s="8"/>
+      <c r="E44" s="3"/>
       <c r="F44" s="13"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -1780,15 +1779,6 @@
     <row r="64" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="65" x14ac:dyDescent="0.35"/>
     <row r="66" x14ac:dyDescent="0.35"/>
-    <row r="67" x14ac:dyDescent="0.35"/>
-    <row r="68" x14ac:dyDescent="0.35"/>
-    <row r="69" x14ac:dyDescent="0.35"/>
-    <row r="70" x14ac:dyDescent="0.35"/>
-    <row r="71" x14ac:dyDescent="0.35"/>
-    <row r="72" x14ac:dyDescent="0.35"/>
-    <row r="73" x14ac:dyDescent="0.35"/>
-    <row r="74" x14ac:dyDescent="0.35"/>
-    <row r="75" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
     <sortCondition descending="1" ref="C1:C74"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D63D98-F650-9540-A2FE-C7BC8D677554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1A12D5-4EA2-FA4D-BDE2-E1448F89A03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -805,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -906,16 +906,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" s="11">
-        <v>47913</v>
+        <v>47939</v>
       </c>
       <c r="D5" s="11">
         <v>51000</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="13"/>
       <c r="G5" s="23"/>
       <c r="H5" s="18" t="s">
         <v>9</v>
@@ -926,36 +924,32 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C6" s="11">
-        <v>47730</v>
+        <v>47913</v>
       </c>
       <c r="D6" s="11">
         <v>51000</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="11">
-        <v>45036</v>
+        <v>47730</v>
       </c>
       <c r="D7" s="11">
-        <v>48000</v>
+        <v>51000</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="13" t="s">
-        <v>63</v>
-      </c>
+      <c r="F7" s="13"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
@@ -964,16 +958,18 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C8" s="11">
-        <v>44967</v>
+        <v>45036</v>
       </c>
       <c r="D8" s="11">
         <v>48000</v>
       </c>
       <c r="E8" s="3"/>
-      <c r="F8" s="13"/>
+      <c r="F8" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
@@ -1503,16 +1499,15 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C39" s="10">
-        <v>15001</v>
+        <v>15036</v>
       </c>
       <c r="D39" s="10">
         <v>18000</v>
       </c>
-      <c r="E39" s="8"/>
-      <c r="F39" s="13"/>
+      <c r="E39" s="3"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
@@ -1521,10 +1516,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C40" s="10">
-        <v>14977</v>
+        <v>15001</v>
       </c>
       <c r="D40" s="10">
         <v>18000</v>
@@ -1539,10 +1534,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C41" s="10">
-        <v>14955</v>
+        <v>14977</v>
       </c>
       <c r="D41" s="10">
         <v>18000</v>
@@ -1557,14 +1552,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C42" s="10">
-        <v>14922</v>
+        <v>14955</v>
       </c>
       <c r="D42" s="10">
         <v>18000</v>
       </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="13"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
@@ -1573,16 +1570,14 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="C43" s="10">
-        <v>14758</v>
+        <v>14922</v>
       </c>
       <c r="D43" s="10">
         <v>18000</v>
       </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="13"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
@@ -1591,10 +1586,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="10">
-        <v>14692</v>
+        <v>14758</v>
       </c>
       <c r="D44" s="10">
         <v>18000</v>
@@ -1609,14 +1604,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C45" s="10">
-        <v>12015</v>
+        <v>14692</v>
       </c>
       <c r="D45" s="10">
-        <v>15000</v>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="13"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
     </row>
@@ -1625,10 +1622,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C46" s="10">
-        <v>11845</v>
+        <v>12015</v>
       </c>
       <c r="D46" s="10">
         <v>15000</v>
@@ -1779,6 +1776,8 @@
     <row r="64" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="65" x14ac:dyDescent="0.35"/>
     <row r="66" x14ac:dyDescent="0.35"/>
+    <row r="67" x14ac:dyDescent="0.35"/>
+    <row r="68" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
     <sortCondition descending="1" ref="C1:C74"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1A12D5-4EA2-FA4D-BDE2-E1448F89A03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4458B1EE-462C-C342-B5CC-4E4A12224333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -805,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -1221,13 +1221,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C23" s="10">
-        <v>24067</v>
+        <v>27004</v>
       </c>
       <c r="D23" s="10">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="13"/>
@@ -1239,13 +1239,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C24" s="10">
-        <v>24062</v>
+        <v>26924</v>
       </c>
       <c r="D24" s="10">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="13"/>
@@ -1257,10 +1257,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C25" s="10">
-        <v>27004</v>
+        <v>26855</v>
       </c>
       <c r="D25" s="10">
         <v>30000</v>
@@ -1275,13 +1275,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C26" s="10">
-        <v>26924</v>
+        <v>24067</v>
       </c>
       <c r="D26" s="10">
-        <v>30000</v>
+        <v>27000</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="13"/>
@@ -1293,10 +1293,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="C27" s="10">
-        <v>23955</v>
+        <v>24062</v>
       </c>
       <c r="D27" s="10">
         <v>27000</v>
@@ -1311,14 +1311,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C28" s="10">
-        <v>23903</v>
+        <v>23955</v>
       </c>
       <c r="D28" s="10">
         <v>27000</v>
       </c>
+      <c r="E28" s="8"/>
+      <c r="F28" s="13"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
@@ -1327,16 +1329,14 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C29" s="10">
-        <v>23837</v>
+        <v>23903</v>
       </c>
       <c r="D29" s="10">
         <v>27000</v>
       </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="13"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
@@ -1773,11 +1773,17 @@
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
     </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35"/>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="65" x14ac:dyDescent="0.35"/>
     <row r="66" x14ac:dyDescent="0.35"/>
     <row r="67" x14ac:dyDescent="0.35"/>
     <row r="68" x14ac:dyDescent="0.35"/>
+    <row r="69" x14ac:dyDescent="0.35"/>
+    <row r="70" x14ac:dyDescent="0.35"/>
+    <row r="71" x14ac:dyDescent="0.35"/>
+    <row r="72" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
     <sortCondition descending="1" ref="C1:C74"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4458B1EE-462C-C342-B5CC-4E4A12224333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D4108A-2EB3-3D40-A965-8DEF777686CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -805,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -847,10 +847,10 @@
         <v>14</v>
       </c>
       <c r="C2" s="11">
-        <v>57062</v>
+        <v>60031</v>
       </c>
       <c r="D2" s="11">
-        <v>60000</v>
+        <v>63000</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" t="s">
@@ -1311,10 +1311,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="C28" s="10">
-        <v>23955</v>
+        <v>24003</v>
       </c>
       <c r="D28" s="10">
         <v>27000</v>
@@ -1329,14 +1329,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C29" s="10">
-        <v>23903</v>
+        <v>23955</v>
       </c>
       <c r="D29" s="10">
         <v>27000</v>
       </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="13"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
@@ -1345,10 +1347,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C30" s="10">
-        <v>23812</v>
+        <v>23903</v>
       </c>
       <c r="D30" s="10">
         <v>27000</v>
@@ -1361,10 +1363,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C31" s="10">
-        <v>23750</v>
+        <v>23812</v>
       </c>
       <c r="D31" s="10">
         <v>27000</v>
@@ -1377,34 +1379,32 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C32" s="10">
-        <v>21210</v>
+        <v>23750</v>
       </c>
       <c r="D32" s="10">
-        <v>24000</v>
-      </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="13"/>
+        <v>27000</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C33" s="10">
-        <v>20987</v>
+        <v>21210</v>
       </c>
       <c r="D33" s="10">
         <v>24000</v>
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="13"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
@@ -1429,10 +1429,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="C35" s="10">
-        <v>18055</v>
+        <v>18092</v>
       </c>
       <c r="D35" s="10">
         <v>21000</v>
@@ -1447,10 +1447,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C36" s="10">
-        <v>17994</v>
+        <v>18055</v>
       </c>
       <c r="D36" s="10">
         <v>21000</v>
@@ -1465,15 +1465,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="C37" s="10">
-        <v>17822</v>
+        <v>17994</v>
       </c>
       <c r="D37" s="10">
         <v>21000</v>
       </c>
       <c r="E37" s="3"/>
+      <c r="F37" s="13"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
@@ -1482,10 +1483,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C38" s="10">
-        <v>17786</v>
+        <v>17822</v>
       </c>
       <c r="D38" s="10">
         <v>21000</v>
@@ -1499,13 +1500,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C39" s="10">
-        <v>15036</v>
+        <v>17786</v>
       </c>
       <c r="D39" s="10">
-        <v>18000</v>
+        <v>21000</v>
       </c>
       <c r="E39" s="3"/>
       <c r="G39" s="4"/>
@@ -1516,16 +1517,15 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C40" s="10">
-        <v>15001</v>
+        <v>15036</v>
       </c>
       <c r="D40" s="10">
         <v>18000</v>
       </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="13"/>
+      <c r="E40" s="3"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
@@ -1534,10 +1534,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C41" s="10">
-        <v>14977</v>
+        <v>15001</v>
       </c>
       <c r="D41" s="10">
         <v>18000</v>
@@ -1552,10 +1552,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C42" s="10">
-        <v>14955</v>
+        <v>14977</v>
       </c>
       <c r="D42" s="10">
         <v>18000</v>
@@ -1570,14 +1570,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C43" s="10">
-        <v>14922</v>
+        <v>14955</v>
       </c>
       <c r="D43" s="10">
         <v>18000</v>
       </c>
+      <c r="E43" s="8"/>
+      <c r="F43" s="13"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
@@ -1776,14 +1778,6 @@
     <row r="62" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35"/>
-    <row r="65" x14ac:dyDescent="0.35"/>
-    <row r="66" x14ac:dyDescent="0.35"/>
-    <row r="67" x14ac:dyDescent="0.35"/>
-    <row r="68" x14ac:dyDescent="0.35"/>
-    <row r="69" x14ac:dyDescent="0.35"/>
-    <row r="70" x14ac:dyDescent="0.35"/>
-    <row r="71" x14ac:dyDescent="0.35"/>
-    <row r="72" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
     <sortCondition descending="1" ref="C1:C74"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D4108A-2EB3-3D40-A965-8DEF777686CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DEC443E-5A4B-F44B-897B-5DA44A7B637F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -805,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -1149,15 +1149,15 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C19" s="10">
-        <v>29989</v>
+        <v>30071</v>
       </c>
       <c r="D19" s="10">
         <v>33000</v>
       </c>
-      <c r="E19" s="8"/>
+      <c r="E19" s="3"/>
       <c r="F19" s="13"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -1167,10 +1167,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C20" s="10">
-        <v>29923</v>
+        <v>29989</v>
       </c>
       <c r="D20" s="10">
         <v>33000</v>
@@ -1185,10 +1185,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C21" s="10">
-        <v>28960</v>
+        <v>29923</v>
       </c>
       <c r="D21" s="10">
         <v>33000</v>
@@ -1203,13 +1203,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C22" s="10">
-        <v>27101</v>
+        <v>28960</v>
       </c>
       <c r="D22" s="10">
-        <v>30000</v>
+        <v>33000</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="13"/>
@@ -1221,10 +1221,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C23" s="10">
-        <v>27004</v>
+        <v>27101</v>
       </c>
       <c r="D23" s="10">
         <v>30000</v>
@@ -1778,6 +1778,7 @@
     <row r="62" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35"/>
+    <row r="65" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
     <sortCondition descending="1" ref="C1:C74"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DEC443E-5A4B-F44B-897B-5DA44A7B637F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297BEB00-C327-D541-ADF8-C234AC21E4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -975,33 +975,34 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C9" s="11">
-        <v>41984</v>
+        <v>42145</v>
       </c>
       <c r="D9" s="11">
         <v>45000</v>
       </c>
-      <c r="E9" s="6"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="13"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="12">
-        <v>39096</v>
-      </c>
-      <c r="D10" s="12">
-        <v>42000</v>
+        <v>8</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="11">
+        <v>41984</v>
+      </c>
+      <c r="D10" s="11">
+        <v>45000</v>
       </c>
       <c r="E10" s="6"/>
       <c r="G10" s="4"/>
@@ -1009,36 +1010,35 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C11" s="12">
-        <v>39038</v>
+        <v>39096</v>
       </c>
       <c r="D11" s="12">
         <v>42000</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="13"/>
+      <c r="E11" s="6"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12" s="12">
-        <v>38912</v>
+        <v>39038</v>
       </c>
       <c r="D12" s="12">
         <v>42000</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="3"/>
       <c r="F12" s="13"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
@@ -1077,67 +1077,67 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C15" s="12">
-        <v>35899</v>
+        <v>36093</v>
       </c>
       <c r="D15" s="12">
         <v>39000</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="13"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="10">
-        <v>33048</v>
-      </c>
-      <c r="D16" s="10">
-        <v>36000</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>66</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="12">
+        <v>35899</v>
+      </c>
+      <c r="D16" s="12">
+        <v>39000</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="13"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C17" s="10">
-        <v>33033</v>
+        <v>33048</v>
       </c>
       <c r="D17" s="10">
         <v>36000</v>
       </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="F17" s="13" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C18" s="10">
-        <v>36093</v>
+        <v>33033</v>
       </c>
       <c r="D18" s="10">
-        <v>39000</v>
+        <v>36000</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="13"/>
@@ -1146,36 +1146,36 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C19" s="10">
-        <v>30071</v>
+        <v>33007</v>
       </c>
       <c r="D19" s="10">
-        <v>33000</v>
-      </c>
-      <c r="E19" s="3"/>
+        <v>36000</v>
+      </c>
+      <c r="E19" s="8"/>
       <c r="F19" s="13"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C20" s="10">
-        <v>29989</v>
+        <v>30071</v>
       </c>
       <c r="D20" s="10">
         <v>33000</v>
       </c>
-      <c r="E20" s="8"/>
+      <c r="E20" s="3"/>
       <c r="F20" s="13"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -1621,45 +1621,47 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C46" s="10">
-        <v>12015</v>
+        <v>12030</v>
       </c>
       <c r="D46" s="10">
         <v>15000</v>
       </c>
+      <c r="E46" s="8"/>
+      <c r="F46" s="13"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C47" s="10">
-        <v>8847</v>
+        <v>12015</v>
       </c>
       <c r="D47" s="10">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C48" s="10">
-        <v>8659</v>
+        <v>8977</v>
       </c>
       <c r="D48" s="10">
         <v>12000</v>
@@ -1671,31 +1673,29 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C49" s="10">
-        <v>8433</v>
+        <v>8847</v>
       </c>
       <c r="D49" s="10">
         <v>12000</v>
       </c>
-      <c r="E49" s="8"/>
-      <c r="F49" s="13"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C50" s="10">
-        <v>8977</v>
+        <v>8659</v>
       </c>
       <c r="D50" s="10">
         <v>12000</v>
@@ -1780,8 +1780,8 @@
     <row r="64" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="65" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:F74">
-    <sortCondition descending="1" ref="C1:C74"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:H54">
+    <sortCondition descending="1" ref="C1:C54"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297BEB00-C327-D541-ADF8-C234AC21E4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D9B5A8-04D0-2D4F-B78E-2A669113581C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -400,7 +400,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -464,10 +464,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -837,7 +843,7 @@
       <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="24"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
@@ -885,73 +891,73 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C4" s="11">
-        <v>50985</v>
+        <v>51002</v>
       </c>
       <c r="D4" s="11">
         <v>54000</v>
       </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="22" t="s">
-        <v>50</v>
-      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C5" s="11">
-        <v>47939</v>
+        <v>50985</v>
       </c>
       <c r="D5" s="11">
-        <v>51000</v>
-      </c>
-      <c r="G5" s="23"/>
-      <c r="H5" s="18" t="s">
-        <v>9</v>
+        <v>54000</v>
+      </c>
+      <c r="G5" s="21"/>
+      <c r="H5" s="22" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C6" s="11">
-        <v>47913</v>
+        <v>47939</v>
       </c>
       <c r="D6" s="11">
         <v>51000</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="13"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="26" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C7" s="11">
-        <v>47730</v>
+        <v>47913</v>
       </c>
       <c r="D7" s="11">
         <v>51000</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="13"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
@@ -1236,13 +1242,13 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C24" s="10">
-        <v>26924</v>
+        <v>27087</v>
       </c>
       <c r="D24" s="10">
         <v>30000</v>
@@ -1254,13 +1260,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C25" s="10">
-        <v>26855</v>
+        <v>26924</v>
       </c>
       <c r="D25" s="10">
         <v>30000</v>
@@ -1272,16 +1278,16 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C26" s="10">
-        <v>24067</v>
+        <v>26855</v>
       </c>
       <c r="D26" s="10">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="13"/>
@@ -1290,13 +1296,13 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27" s="10">
-        <v>24062</v>
+        <v>24067</v>
       </c>
       <c r="D27" s="10">
         <v>27000</v>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D9B5A8-04D0-2D4F-B78E-2A669113581C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C50E309-8947-6741-9413-DE90FD0F1B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1486,30 +1486,31 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C38" s="10">
-        <v>17822</v>
+        <v>17906</v>
       </c>
       <c r="D38" s="10">
         <v>21000</v>
       </c>
       <c r="E38" s="3"/>
+      <c r="F38" s="13"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C39" s="10">
-        <v>17786</v>
+        <v>17822</v>
       </c>
       <c r="D39" s="10">
         <v>21000</v>
@@ -1520,16 +1521,16 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C40" s="10">
-        <v>15036</v>
+        <v>17786</v>
       </c>
       <c r="D40" s="10">
-        <v>18000</v>
+        <v>21000</v>
       </c>
       <c r="E40" s="3"/>
       <c r="G40" s="4"/>
@@ -1537,31 +1538,30 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C41" s="10">
-        <v>15001</v>
+        <v>15036</v>
       </c>
       <c r="D41" s="10">
         <v>18000</v>
       </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="13"/>
+      <c r="E41" s="3"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C42" s="10">
-        <v>14977</v>
+        <v>15001</v>
       </c>
       <c r="D42" s="10">
         <v>18000</v>
@@ -1573,13 +1573,13 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C43" s="10">
-        <v>14955</v>
+        <v>14977</v>
       </c>
       <c r="D43" s="10">
         <v>18000</v>
@@ -1591,18 +1591,18 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C44" s="10">
-        <v>14758</v>
+        <v>14955</v>
       </c>
       <c r="D44" s="10">
         <v>18000</v>
       </c>
-      <c r="E44" s="3"/>
+      <c r="E44" s="8"/>
       <c r="F44" s="13"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C50E309-8947-6741-9413-DE90FD0F1B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19BAB108-0E90-DA4C-A238-8EC8BC8C43A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
   <si>
     <t>No.</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>Steering Stem was never replaced during accident repair &amp; Oil leak on the Right cover</t>
+  </si>
+  <si>
+    <t>Accident repairs with a substandard touch</t>
   </si>
 </sst>
 </file>
@@ -400,7 +403,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -458,12 +461,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -474,6 +471,13 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -843,7 +847,7 @@
       <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="23"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
@@ -891,73 +895,75 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C4" s="11">
-        <v>51002</v>
+        <v>51007</v>
       </c>
       <c r="D4" s="11">
         <v>54000</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="13"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C5" s="11">
-        <v>50985</v>
+        <v>51002</v>
       </c>
       <c r="D5" s="11">
         <v>54000</v>
       </c>
-      <c r="G5" s="21"/>
-      <c r="H5" s="22" t="s">
-        <v>50</v>
-      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C6" s="11">
-        <v>47939</v>
+        <v>50985</v>
       </c>
       <c r="D6" s="11">
-        <v>51000</v>
-      </c>
-      <c r="G6" s="25"/>
-      <c r="H6" s="26" t="s">
-        <v>9</v>
+        <v>54000</v>
+      </c>
+      <c r="G6" s="26"/>
+      <c r="H6" s="27" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="11">
-        <v>47913</v>
+        <v>47939</v>
       </c>
       <c r="D7" s="11">
         <v>51000</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="13"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
@@ -981,51 +987,52 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" s="11">
-        <v>42145</v>
+        <v>44912</v>
       </c>
       <c r="D9" s="11">
-        <v>45000</v>
-      </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+        <v>48000</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="13" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C10" s="11">
-        <v>41984</v>
+        <v>42145</v>
       </c>
       <c r="D10" s="11">
         <v>45000</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="13"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>9</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="12">
-        <v>39096</v>
-      </c>
-      <c r="D11" s="12">
-        <v>42000</v>
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="11">
+        <v>41984</v>
+      </c>
+      <c r="D11" s="11">
+        <v>45000</v>
       </c>
       <c r="E11" s="6"/>
       <c r="G11" s="4"/>
@@ -1033,37 +1040,38 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C12" s="12">
-        <v>39038</v>
+        <v>39096</v>
       </c>
       <c r="D12" s="12">
         <v>42000</v>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="13"/>
+      <c r="E12" s="6"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="12">
-        <v>38901</v>
+        <v>39038</v>
       </c>
       <c r="D13" s="12">
         <v>42000</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="13"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
@@ -1260,31 +1268,29 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="C25" s="10">
-        <v>26924</v>
+        <v>26978</v>
       </c>
       <c r="D25" s="10">
         <v>30000</v>
       </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="13"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C26" s="10">
-        <v>26855</v>
+        <v>26924</v>
       </c>
       <c r="D26" s="10">
         <v>30000</v>
@@ -1296,16 +1302,16 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C27" s="10">
-        <v>24067</v>
+        <v>26855</v>
       </c>
       <c r="D27" s="10">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="13"/>
@@ -1314,13 +1320,13 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C28" s="10">
-        <v>24003</v>
+        <v>24067</v>
       </c>
       <c r="D28" s="10">
         <v>27000</v>
@@ -1332,13 +1338,13 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="C29" s="10">
-        <v>23955</v>
+        <v>24003</v>
       </c>
       <c r="D29" s="10">
         <v>27000</v>
@@ -1350,17 +1356,19 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C30" s="10">
-        <v>23903</v>
+        <v>23955</v>
       </c>
       <c r="D30" s="10">
         <v>27000</v>
       </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="13"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19BAB108-0E90-DA4C-A238-8EC8BC8C43A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE3D7BA-9768-4A45-94F2-9A1EE8FBADCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -474,10 +474,10 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1669,16 +1669,16 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C48" s="10">
-        <v>8977</v>
+        <v>11897</v>
       </c>
       <c r="D48" s="10">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="E48" s="8"/>
       <c r="F48" s="13"/>
@@ -1687,35 +1687,35 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C49" s="10">
-        <v>8847</v>
+        <v>8977</v>
       </c>
       <c r="D49" s="10">
         <v>12000</v>
       </c>
+      <c r="E49" s="8"/>
+      <c r="F49" s="13"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C50" s="10">
-        <v>8659</v>
+        <v>8847</v>
       </c>
       <c r="D50" s="10">
         <v>12000</v>
       </c>
-      <c r="E50" s="8"/>
-      <c r="F50" s="13"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
     </row>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE3D7BA-9768-4A45-94F2-9A1EE8FBADCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52ED434-DD1E-514A-941D-E722AA0EED0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1075,37 +1075,37 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C14" s="12">
-        <v>36148</v>
+        <v>38957</v>
       </c>
       <c r="D14" s="12">
-        <v>39000</v>
+        <v>42000</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="13"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C15" s="12">
-        <v>36093</v>
+        <v>36148</v>
       </c>
       <c r="D15" s="12">
         <v>39000</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="13"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
@@ -1178,36 +1178,36 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C20" s="10">
-        <v>30071</v>
+        <v>32962</v>
       </c>
       <c r="D20" s="10">
-        <v>33000</v>
-      </c>
-      <c r="E20" s="3"/>
+        <v>36000</v>
+      </c>
+      <c r="E20" s="8"/>
       <c r="F20" s="13"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C21" s="10">
-        <v>29923</v>
+        <v>30071</v>
       </c>
       <c r="D21" s="10">
         <v>33000</v>
       </c>
-      <c r="E21" s="8"/>
+      <c r="E21" s="3"/>
       <c r="F21" s="13"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
@@ -1458,31 +1458,31 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C36" s="10">
-        <v>18055</v>
+        <v>18072</v>
       </c>
       <c r="D36" s="10">
         <v>21000</v>
       </c>
-      <c r="E36" s="3"/>
+      <c r="E36" s="8"/>
       <c r="F36" s="13"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C37" s="10">
-        <v>17994</v>
+        <v>18055</v>
       </c>
       <c r="D37" s="10">
         <v>21000</v>
@@ -1494,13 +1494,13 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C38" s="10">
-        <v>17906</v>
+        <v>17994</v>
       </c>
       <c r="D38" s="10">
         <v>21000</v>
@@ -1512,30 +1512,31 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C39" s="10">
-        <v>17822</v>
+        <v>17906</v>
       </c>
       <c r="D39" s="10">
         <v>21000</v>
       </c>
       <c r="E39" s="3"/>
+      <c r="F39" s="13"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C40" s="10">
-        <v>17786</v>
+        <v>17822</v>
       </c>
       <c r="D40" s="10">
         <v>21000</v>
@@ -1546,16 +1547,16 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C41" s="10">
-        <v>15036</v>
+        <v>17786</v>
       </c>
       <c r="D41" s="10">
-        <v>18000</v>
+        <v>21000</v>
       </c>
       <c r="E41" s="3"/>
       <c r="G41" s="4"/>
@@ -1563,19 +1564,18 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C42" s="10">
-        <v>15001</v>
+        <v>15036</v>
       </c>
       <c r="D42" s="10">
         <v>18000</v>
       </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="13"/>
+      <c r="E42" s="3"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52ED434-DD1E-514A-941D-E722AA0EED0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01931F31-1AFA-8847-B2C9-B872282FFA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -973,10 +973,10 @@
         <v>24</v>
       </c>
       <c r="C8" s="11">
-        <v>45036</v>
+        <v>47838</v>
       </c>
       <c r="D8" s="11">
-        <v>48000</v>
+        <v>51000</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="13" t="s">
@@ -1374,29 +1374,31 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C31" s="10">
-        <v>23812</v>
+        <v>23891</v>
       </c>
       <c r="D31" s="10">
         <v>27000</v>
       </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="13"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C32" s="10">
-        <v>23750</v>
+        <v>23812</v>
       </c>
       <c r="D32" s="10">
         <v>27000</v>
@@ -1406,37 +1408,35 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C33" s="10">
-        <v>21210</v>
+        <v>23750</v>
       </c>
       <c r="D33" s="10">
-        <v>24000</v>
-      </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="13"/>
+        <v>27000</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="C34" s="10">
-        <v>20842</v>
+        <v>21210</v>
       </c>
       <c r="D34" s="10">
         <v>24000</v>
       </c>
-      <c r="E34" s="3"/>
+      <c r="E34" s="8"/>
       <c r="F34" s="13"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2">

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01931F31-1AFA-8847-B2C9-B872282FFA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B6C13C-00E3-5549-B491-D24DC5E3CA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -895,7 +895,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>16</v>
@@ -913,7 +913,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>23</v>
@@ -931,7 +931,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>28</v>
@@ -949,7 +949,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>7</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>30</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>32</v>
@@ -1023,33 +1023,34 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11">
-        <v>41984</v>
+        <v>42037</v>
       </c>
       <c r="D11" s="11">
         <v>45000</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="13"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>9</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="12">
-        <v>39096</v>
-      </c>
-      <c r="D12" s="12">
-        <v>42000</v>
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="11">
+        <v>41984</v>
+      </c>
+      <c r="D12" s="11">
+        <v>45000</v>
       </c>
       <c r="E12" s="6"/>
       <c r="G12" s="4"/>
@@ -1057,25 +1058,24 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C13" s="12">
-        <v>39038</v>
+        <v>39096</v>
       </c>
       <c r="D13" s="12">
         <v>42000</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="13"/>
+      <c r="E13" s="6"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>15</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>18</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>27</v>
@@ -1125,7 +1125,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>13</v>
@@ -1142,7 +1142,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>21</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>48</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>31</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>43</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>41</v>
@@ -1268,7 +1268,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>49</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>45</v>
@@ -1320,31 +1320,29 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C28" s="10">
-        <v>24067</v>
+        <v>24116</v>
       </c>
       <c r="D28" s="10">
         <v>27000</v>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="13"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C29" s="10">
-        <v>24003</v>
+        <v>24067</v>
       </c>
       <c r="D29" s="10">
         <v>27000</v>
@@ -1356,13 +1354,13 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="C30" s="10">
-        <v>23955</v>
+        <v>24003</v>
       </c>
       <c r="D30" s="10">
         <v>27000</v>
@@ -1374,47 +1372,49 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C31" s="10">
-        <v>23891</v>
+        <v>23955</v>
       </c>
       <c r="D31" s="10">
         <v>27000</v>
       </c>
-      <c r="E31" s="3"/>
+      <c r="E31" s="8"/>
       <c r="F31" s="13"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C32" s="10">
-        <v>23812</v>
+        <v>23891</v>
       </c>
       <c r="D32" s="10">
         <v>27000</v>
       </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="13"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C33" s="10">
-        <v>23750</v>
+        <v>23812</v>
       </c>
       <c r="D33" s="10">
         <v>27000</v>
@@ -1424,19 +1424,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C34" s="10">
-        <v>21210</v>
+        <v>23750</v>
       </c>
       <c r="D34" s="10">
-        <v>24000</v>
-      </c>
-      <c r="E34" s="8"/>
-      <c r="F34" s="13"/>
+        <v>27000</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
@@ -1458,7 +1458,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>52</v>
@@ -1476,7 +1476,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>44</v>
@@ -1512,7 +1512,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>26</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>11</v>
@@ -1547,7 +1547,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>42</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>57</v>
@@ -1581,7 +1581,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>56</v>
@@ -1599,7 +1599,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>38</v>
@@ -1635,7 +1635,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>46</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>54</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>36</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>53</v>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B6C13C-00E3-5549-B491-D24DC5E3CA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E40AD1-5220-874D-9146-037064DEAE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1530,30 +1530,31 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="C40" s="10">
-        <v>17822</v>
+        <v>17868</v>
       </c>
       <c r="D40" s="10">
         <v>21000</v>
       </c>
-      <c r="E40" s="3"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="13"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C41" s="10">
-        <v>17786</v>
+        <v>17822</v>
       </c>
       <c r="D41" s="10">
         <v>21000</v>
@@ -1564,16 +1565,16 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C42" s="10">
-        <v>15036</v>
+        <v>17786</v>
       </c>
       <c r="D42" s="10">
-        <v>18000</v>
+        <v>21000</v>
       </c>
       <c r="E42" s="3"/>
       <c r="G42" s="4"/>
@@ -1581,19 +1582,18 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C43" s="10">
-        <v>14977</v>
+        <v>15036</v>
       </c>
       <c r="D43" s="10">
         <v>18000</v>
       </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="13"/>
+      <c r="E43" s="3"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E40AD1-5220-874D-9146-037064DEAE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8A808A-6776-5B42-8CF0-F6900BC7365E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -879,10 +879,10 @@
         <v>19</v>
       </c>
       <c r="C3" s="11">
-        <v>53901</v>
+        <v>56725</v>
       </c>
       <c r="D3" s="11">
-        <v>57000</v>
+        <v>60000</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" t="s">
@@ -1093,29 +1093,29 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C15" s="12">
-        <v>36148</v>
+        <v>38919</v>
       </c>
       <c r="D15" s="12">
-        <v>39000</v>
+        <v>42000</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="13"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C16" s="12">
-        <v>35899</v>
+        <v>36148</v>
       </c>
       <c r="D16" s="12">
         <v>39000</v>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8A808A-6776-5B42-8CF0-F6900BC7365E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4C2B29-F795-9E45-B244-442455967A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="68">
   <si>
     <t>No.</t>
   </si>
@@ -937,10 +937,10 @@
         <v>28</v>
       </c>
       <c r="C6" s="11">
-        <v>50985</v>
+        <v>53997</v>
       </c>
       <c r="D6" s="11">
-        <v>54000</v>
+        <v>57000</v>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="27" t="s">
@@ -1105,7 +1105,9 @@
         <v>42000</v>
       </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="13"/>
+      <c r="F15" s="13" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
